--- a/public/reports/weekly_briefing/2026-09-14.xlsx
+++ b/public/reports/weekly_briefing/2026-09-14.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$O$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,13 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;;0.0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="+0;-0;0"/>
     <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
     <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
-    <numFmt numFmtId="168" formatCode="+0.0;-0.0;0.0"/>
-    <numFmt numFmtId="169" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="168" formatCode="+0.00;-0.00;0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -430,14 +431,8 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -457,16 +452,13 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -478,19 +470,19 @@
     <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -505,16 +497,25 @@
     <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -972,7 +973,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14 16:13 KST</t>
+          <t>2026-09-14 22:50 KST</t>
         </is>
       </c>
     </row>
@@ -985,7 +986,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체 투심 악화와 외국인 대규모 매도에 따른 지수 급락</t>
+          <t>AI 속도조절론 부각에 따른 반도체 급락과 외국인 대규모 매도</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1631,7 @@
               <color rgb="00D64545"/>
               <sz val="10"/>
             </rPr>
-            <t>209▲ 상한2</t>
+            <t>295▲ 상한2</t>
           </r>
           <r>
             <t>/</t>
@@ -1641,7 +1642,7 @@
               <color rgb="003182F6"/>
               <sz val="10"/>
             </rPr>
-            <t>289▼</t>
+            <t>498▼</t>
           </r>
         </is>
       </c>
@@ -1656,7 +1657,7 @@
               <color rgb="00D64545"/>
               <sz val="10"/>
             </rPr>
-            <t>449▲ 상한6</t>
+            <t>627▲ 상한7</t>
           </r>
           <r>
             <t>/</t>
@@ -1667,7 +1668,7 @@
               <color rgb="003182F6"/>
               <sz val="10"/>
             </rPr>
-            <t>513▼</t>
+            <t>900▼</t>
           </r>
         </is>
       </c>
@@ -1678,7 +1679,7 @@
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>미국 증시의 기술주 반등과 CPI 예상치 부합에도 불구하고, 국내 증시는 'AI 속도조절론'이 부각되며 반도체 대형주 중심의 외국인 매도세가 쏟아져 지수가 급락함.</t>
+          <t>미국 증시는 CPI 예상치 부합으로 상승했으나, 국내 증시는 'AI 속도조절론'이 부각되며 반도체 중심의 외국인 매도세가 쏟아져 급락함.</t>
         </is>
       </c>
     </row>
@@ -1719,21 +1720,21 @@
     <row r="37" ht="31" customHeight="1" s="15">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>- 미국 8월 CPI는 전년 대비 3.4%로 예상치에 부합했으나, 미시간대 소비자심리지수가 47.8로 예상치(51.0)를 하회하며 매크로 환경의 불확실성이 잔존함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="31" customHeight="1" s="15">
+          <t>- 미국 8월 CPI는 3.4%로 예상치에 부합했으나, 미시간대 소비자심리지수는 47.8로 예상치(51.0)를 하회하며 매크로 환경의 불확실성이 잔존함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="15">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서 전기·전자 섹터에 외국인 매도세가 집중되며 지수 하락을 견인했고, 반면 운송·창고(순매수 224억)와 오락·문화(순매수 49억) 등 일부 섹터로 수급이 분산되는 양상을 보임.</t>
+          <t>- 수급 측면에서 외국인은 전기·전자 섹터에 매도를 집중하며 코스피 3.3조 원 순매도를 기록, 지수 하락의 핵심 동인으로 작용함.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 대규모 매도세 진정 여부와 반도체 수출입 확정치가 향후 증시 반등의 핵심 변수로 작용할 전망.</t>
+          <t>- 매크로 지표보다 AI 산업에 대한 센티먼트 변화가 시장 수급을 지배하는 국면임.</t>
         </is>
       </c>
     </row>
@@ -1840,24 +1841,28 @@
         </is>
       </c>
       <c r="E43" s="28" t="n">
-        <v>397</v>
+        <v>482</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>431</v>
+        <v>528</v>
       </c>
       <c r="G43" s="29" t="n">
-        <v>-34</v>
+        <v>-46</v>
       </c>
       <c r="H43" s="29" t="n">
-        <v>-393</v>
+        <v>-478</v>
       </c>
       <c r="I43" s="31" t="n">
         <v>88.8</v>
       </c>
-      <c r="J43" s="31" t="inlineStr"/>
-      <c r="K43" s="31" t="inlineStr"/>
-    </row>
-    <row r="44">
+      <c r="J43" s="31" t="n">
+        <v>5185.7</v>
+      </c>
+      <c r="K43" s="31" t="n">
+        <v>142.2</v>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1" s="15">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
@@ -1866,9 +1871,9 @@
       <c r="B44" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="31" t="inlineStr">
-        <is>
-          <t>삼성중공업</t>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -1877,24 +1882,28 @@
         </is>
       </c>
       <c r="E44" s="28" t="n">
-        <v>285</v>
+        <v>393</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>104</v>
+        <v>278</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="H44" s="29" t="n">
-        <v>-287</v>
+        <v>-422</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J44" s="31" t="inlineStr"/>
-      <c r="K44" s="31" t="inlineStr"/>
-    </row>
-    <row r="45" ht="31" customHeight="1" s="15">
+        <v>368.3</v>
+      </c>
+      <c r="J44" s="31" t="n">
+        <v>13145</v>
+      </c>
+      <c r="K44" s="31" t="n">
+        <v>723.8</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
@@ -1903,9 +1912,9 @@
       <c r="B45" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D45" s="35" t="inlineStr">
@@ -1914,22 +1923,26 @@
         </is>
       </c>
       <c r="E45" s="28" t="n">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="F45" s="28" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="G45" s="28" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="H45" s="29" t="n">
-        <v>-295</v>
+        <v>-335</v>
       </c>
       <c r="I45" s="31" t="n">
-        <v>367.9</v>
-      </c>
-      <c r="J45" s="31" t="inlineStr"/>
-      <c r="K45" s="31" t="inlineStr"/>
+        <v>28.8</v>
+      </c>
+      <c r="J45" s="31" t="n">
+        <v>7990.5</v>
+      </c>
+      <c r="K45" s="31" t="n">
+        <v>145.9</v>
+      </c>
     </row>
     <row r="46" ht="31" customHeight="1" s="15">
       <c r="A46" s="8" t="inlineStr">
@@ -1951,22 +1964,26 @@
         </is>
       </c>
       <c r="E46" s="28" t="n">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="G46" s="28" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H46" s="29" t="n">
-        <v>-220</v>
+        <v>-262</v>
       </c>
       <c r="I46" s="31" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="J46" s="31" t="inlineStr"/>
-      <c r="K46" s="31" t="inlineStr"/>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="J46" s="31" t="n">
+        <v>6319.8</v>
+      </c>
+      <c r="K46" s="31" t="n">
+        <v>114.4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -1988,22 +2005,26 @@
         </is>
       </c>
       <c r="E47" s="28" t="n">
-        <v>221</v>
-      </c>
-      <c r="F47" s="29" t="n">
-        <v>-1</v>
+        <v>228</v>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>12</v>
       </c>
       <c r="G47" s="28" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H47" s="29" t="n">
-        <v>-218</v>
+        <v>-223</v>
       </c>
       <c r="I47" s="31" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="J47" s="31" t="inlineStr"/>
-      <c r="K47" s="31" t="inlineStr"/>
+        <v>52.3</v>
+      </c>
+      <c r="J47" s="31" t="n">
+        <v>7805.8</v>
+      </c>
+      <c r="K47" s="31" t="n">
+        <v>206.4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -2034,13 +2055,17 @@
         <v>78</v>
       </c>
       <c r="H48" s="29" t="n">
-        <v>-159</v>
+        <v>-158</v>
       </c>
       <c r="I48" s="31" t="n">
         <v>22.6</v>
       </c>
-      <c r="J48" s="31" t="inlineStr"/>
-      <c r="K48" s="31" t="inlineStr"/>
+      <c r="J48" s="31" t="n">
+        <v>1755.7</v>
+      </c>
+      <c r="K48" s="31" t="n">
+        <v>41.9</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -2062,22 +2087,26 @@
         </is>
       </c>
       <c r="E49" s="28" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="F49" s="29" t="n">
-        <v>-29</v>
+        <v>-9</v>
       </c>
       <c r="G49" s="28" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H49" s="29" t="n">
-        <v>-121</v>
+        <v>-136</v>
       </c>
       <c r="I49" s="31" t="n">
         <v>43.9</v>
       </c>
-      <c r="J49" s="31" t="inlineStr"/>
-      <c r="K49" s="31" t="inlineStr"/>
+      <c r="J49" s="31" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K49" s="31" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -2099,22 +2128,26 @@
         </is>
       </c>
       <c r="E50" s="28" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F50" s="29" t="n">
-        <v>-52</v>
+        <v>-41</v>
       </c>
       <c r="G50" s="28" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H50" s="29" t="n">
-        <v>-118</v>
+        <v>-125</v>
       </c>
       <c r="I50" s="31" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="J50" s="31" t="inlineStr"/>
-      <c r="K50" s="31" t="inlineStr"/>
+        <v>35.9</v>
+      </c>
+      <c r="J50" s="31" t="n">
+        <v>5479.1</v>
+      </c>
+      <c r="K50" s="31" t="n">
+        <v>589.4</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -2127,7 +2160,7 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="D51" s="35" t="inlineStr">
@@ -2136,22 +2169,26 @@
         </is>
       </c>
       <c r="E51" s="28" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G51" s="29" t="n">
-        <v>-33</v>
+        <v>-11</v>
       </c>
       <c r="H51" s="29" t="n">
-        <v>-101</v>
+        <v>-124</v>
       </c>
       <c r="I51" s="31" t="n">
-        <v>161</v>
-      </c>
-      <c r="J51" s="31" t="inlineStr"/>
-      <c r="K51" s="31" t="inlineStr"/>
+        <v>52.7</v>
+      </c>
+      <c r="J51" s="31" t="n">
+        <v>3925.9</v>
+      </c>
+      <c r="K51" s="31" t="n">
+        <v>-107.3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -2173,22 +2210,26 @@
         </is>
       </c>
       <c r="E52" s="28" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>-244</v>
+        <v>-239</v>
       </c>
       <c r="H52" s="29" t="n">
-        <v>-71</v>
+        <v>-85</v>
       </c>
       <c r="I52" s="31" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="J52" s="31" t="inlineStr"/>
-      <c r="K52" s="31" t="inlineStr"/>
+      <c r="J52" s="31" t="n">
+        <v>12346.5</v>
+      </c>
+      <c r="K52" s="31" t="n">
+        <v>-750.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -2210,22 +2251,26 @@
         </is>
       </c>
       <c r="E53" s="29" t="n">
-        <v>-25157</v>
+        <v>-30101</v>
       </c>
       <c r="F53" s="29" t="n">
-        <v>-20586</v>
+        <v>-23962</v>
       </c>
       <c r="G53" s="29" t="n">
-        <v>-4571</v>
+        <v>-6139</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>15259</v>
+        <v>20306</v>
       </c>
       <c r="I53" s="31" t="n">
-        <v>7736.1</v>
-      </c>
-      <c r="J53" s="31" t="inlineStr"/>
-      <c r="K53" s="31" t="inlineStr"/>
+        <v>7751.2</v>
+      </c>
+      <c r="J53" s="31" t="n">
+        <v>205396.7</v>
+      </c>
+      <c r="K53" s="31" t="n">
+        <v>-14617.4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -2247,22 +2292,26 @@
         </is>
       </c>
       <c r="E54" s="29" t="n">
-        <v>-12891</v>
+        <v>-17666</v>
       </c>
       <c r="F54" s="29" t="n">
-        <v>-8440</v>
+        <v>-10512</v>
       </c>
       <c r="G54" s="29" t="n">
-        <v>-4451</v>
+        <v>-7154</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>8616</v>
+        <v>13639</v>
       </c>
       <c r="I54" s="31" t="n">
-        <v>3656.9</v>
-      </c>
-      <c r="J54" s="31" t="inlineStr"/>
-      <c r="K54" s="31" t="inlineStr"/>
+        <v>3677</v>
+      </c>
+      <c r="J54" s="31" t="n">
+        <v>223221.9</v>
+      </c>
+      <c r="K54" s="31" t="n">
+        <v>-8156.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -2275,7 +2324,7 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D55" s="35" t="inlineStr">
@@ -2284,22 +2333,26 @@
         </is>
       </c>
       <c r="E55" s="29" t="n">
-        <v>-2027</v>
+        <v>-2389</v>
       </c>
       <c r="F55" s="29" t="n">
-        <v>-2038</v>
-      </c>
-      <c r="G55" s="28" t="n">
-        <v>11</v>
+        <v>-1503</v>
+      </c>
+      <c r="G55" s="29" t="n">
+        <v>-886</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>2006</v>
+        <v>2354</v>
       </c>
       <c r="I55" s="31" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J55" s="31" t="inlineStr"/>
-      <c r="K55" s="31" t="inlineStr"/>
+        <v>522.7</v>
+      </c>
+      <c r="J55" s="31" t="n">
+        <v>32675</v>
+      </c>
+      <c r="K55" s="31" t="n">
+        <v>-571</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -2312,31 +2365,35 @@
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D56" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E56" s="29" t="n">
-        <v>-2013</v>
+        <v>-2246</v>
       </c>
       <c r="F56" s="29" t="n">
-        <v>-1317</v>
+        <v>-941</v>
       </c>
       <c r="G56" s="29" t="n">
-        <v>-696</v>
+        <v>-1304</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>1988</v>
+        <v>2197</v>
       </c>
       <c r="I56" s="31" t="n">
-        <v>522.6</v>
-      </c>
-      <c r="J56" s="31" t="inlineStr"/>
-      <c r="K56" s="31" t="inlineStr"/>
+        <v>282.4</v>
+      </c>
+      <c r="J56" s="31" t="n">
+        <v>27337.7</v>
+      </c>
+      <c r="K56" s="31" t="n">
+        <v>-1780.6</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -2349,31 +2406,35 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D57" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E57" s="29" t="n">
-        <v>-1773</v>
+        <v>-2085</v>
       </c>
       <c r="F57" s="29" t="n">
-        <v>-599</v>
-      </c>
-      <c r="G57" s="29" t="n">
-        <v>-1174</v>
+        <v>-2095</v>
+      </c>
+      <c r="G57" s="28" t="n">
+        <v>10</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>1726</v>
+        <v>2057</v>
       </c>
       <c r="I57" s="31" t="n">
-        <v>278.9</v>
-      </c>
-      <c r="J57" s="31" t="inlineStr"/>
-      <c r="K57" s="31" t="inlineStr"/>
+        <v>63.5</v>
+      </c>
+      <c r="J57" s="31" t="n">
+        <v>26514</v>
+      </c>
+      <c r="K57" s="31" t="n">
+        <v>-1435.9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -2395,22 +2456,26 @@
         </is>
       </c>
       <c r="E58" s="29" t="n">
-        <v>-921</v>
+        <v>-1184</v>
       </c>
       <c r="F58" s="29" t="n">
-        <v>-451</v>
+        <v>-637</v>
       </c>
       <c r="G58" s="29" t="n">
-        <v>-470</v>
+        <v>-547</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>947</v>
+        <v>1221</v>
       </c>
       <c r="I58" s="31" t="n">
-        <v>643.4</v>
-      </c>
-      <c r="J58" s="31" t="inlineStr"/>
-      <c r="K58" s="31" t="inlineStr"/>
+        <v>643.7</v>
+      </c>
+      <c r="J58" s="31" t="n">
+        <v>19002.7</v>
+      </c>
+      <c r="K58" s="31" t="n">
+        <v>-860.3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -2432,22 +2497,26 @@
         </is>
       </c>
       <c r="E59" s="29" t="n">
-        <v>-380</v>
+        <v>-526</v>
       </c>
       <c r="F59" s="29" t="n">
-        <v>-195</v>
+        <v>-272</v>
       </c>
       <c r="G59" s="29" t="n">
-        <v>-185</v>
+        <v>-254</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>387</v>
+        <v>533</v>
       </c>
       <c r="I59" s="31" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="J59" s="31" t="inlineStr"/>
-      <c r="K59" s="31" t="inlineStr"/>
+        <v>142.6</v>
+      </c>
+      <c r="J59" s="31" t="n">
+        <v>5242.8</v>
+      </c>
+      <c r="K59" s="31" t="n">
+        <v>-664.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -2469,22 +2538,26 @@
         </is>
       </c>
       <c r="E60" s="29" t="n">
-        <v>-374</v>
+        <v>-461</v>
       </c>
       <c r="F60" s="29" t="n">
-        <v>-234</v>
+        <v>-291</v>
       </c>
       <c r="G60" s="29" t="n">
-        <v>-140</v>
+        <v>-170</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>340</v>
+        <v>424</v>
       </c>
       <c r="I60" s="31" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="J60" s="31" t="inlineStr"/>
-      <c r="K60" s="31" t="inlineStr"/>
+        <v>49.6</v>
+      </c>
+      <c r="J60" s="31" t="n">
+        <v>6549.8</v>
+      </c>
+      <c r="K60" s="31" t="n">
+        <v>-613.2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -2506,22 +2579,26 @@
         </is>
       </c>
       <c r="E61" s="29" t="n">
-        <v>-330</v>
+        <v>-395</v>
       </c>
       <c r="F61" s="29" t="n">
-        <v>-339</v>
-      </c>
-      <c r="G61" s="28" t="n">
-        <v>9</v>
+        <v>-379</v>
+      </c>
+      <c r="G61" s="29" t="n">
+        <v>-15</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="I61" s="31" t="n">
         <v>66.3</v>
       </c>
-      <c r="J61" s="31" t="inlineStr"/>
-      <c r="K61" s="31" t="inlineStr"/>
+      <c r="J61" s="31" t="n">
+        <v>13931.3</v>
+      </c>
+      <c r="K61" s="31" t="n">
+        <v>-442.4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -2534,31 +2611,35 @@
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D62" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E62" s="29" t="n">
-        <v>-248</v>
+        <v>-381</v>
       </c>
       <c r="F62" s="28" t="n">
-        <v>218</v>
+        <v>46</v>
       </c>
       <c r="G62" s="29" t="n">
-        <v>-466</v>
+        <v>-427</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>252</v>
+        <v>390</v>
       </c>
       <c r="I62" s="31" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="J62" s="31" t="inlineStr"/>
-      <c r="K62" s="31" t="inlineStr"/>
+        <v>434.8</v>
+      </c>
+      <c r="J62" s="31" t="n">
+        <v>29634.7</v>
+      </c>
+      <c r="K62" s="31" t="n">
+        <v>-1292.1</v>
+      </c>
     </row>
     <row r="63"/>
     <row r="64">
@@ -2598,10 +2679,10 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="31" customHeight="1" s="15">
+    <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B66" s="35" t="inlineStr">
@@ -2610,42 +2691,42 @@
         </is>
       </c>
       <c r="C66" s="37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" s="31" t="inlineStr"/>
       <c r="E66" s="31" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
-        </is>
-      </c>
-      <c r="H66" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="I66" s="39" t="n">
-        <v>2</v>
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="I66" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="J66" s="31" t="inlineStr"/>
       <c r="K66" s="31" t="inlineStr"/>
     </row>
-    <row r="67" ht="31" customHeight="1" s="15">
+    <row r="67" ht="44.5" customHeight="1" s="15">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>외국인 +80억 순매수, 기관 +78억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +41억 순매수, 기관 +52억 순매수, 대차잔고 -6억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>외국인 +104억 순매수, 기관 +181억 순매수 — 운송장비·부품(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="31" customHeight="1" s="15">
+          <t>외국인 +17억 순매수, 기관 +53억 순매수, 대차잔고 -434억 감소 — 금속(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대한해운</t>
         </is>
       </c>
       <c r="B68" s="35" t="inlineStr">
@@ -2658,9 +2739,9 @@
       </c>
       <c r="D68" s="31" t="inlineStr"/>
       <c r="E68" s="31" t="inlineStr"/>
-      <c r="G68" s="40" t="inlineStr">
-        <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>삼아알미늄</t>
         </is>
       </c>
       <c r="H68" s="35" t="inlineStr">
@@ -2668,8 +2749,8 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="I68" s="39" t="n">
-        <v>2</v>
+      <c r="I68" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="J68" s="31" t="inlineStr"/>
       <c r="K68" s="31" t="inlineStr"/>
@@ -2677,19 +2758,19 @@
     <row r="69" ht="31" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>외국인 +25억 순매수, 기관 +57억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +2억 순매수, 대차잔고 0억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G69" s="17" t="inlineStr">
         <is>
-          <t>외국인 +148억 순매수, 기관 +76억 순매수 — 금속(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="31" customHeight="1" s="15">
+          <t>외국인 +4억 순매수, 기관 +9억 순매수, 대차잔고 -3억 감소 — 금속(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>CJ대한통운</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B70" s="35" t="inlineStr">
@@ -2698,42 +2779,42 @@
         </is>
       </c>
       <c r="C70" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" s="31" t="inlineStr"/>
       <c r="E70" s="31" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>한화오션</t>
-        </is>
-      </c>
-      <c r="H70" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="I70" s="39" t="n">
-        <v>2</v>
+          <t>삼성에스디에스</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="I70" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="J70" s="31" t="inlineStr"/>
       <c r="K70" s="31" t="inlineStr"/>
     </row>
-    <row r="71" ht="31" customHeight="1" s="15">
+    <row r="71" ht="44.5" customHeight="1" s="15">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t>외국인 +11억 순매수, 기관 +0억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +80억 순매수, 기관 +78억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
-          <t>외국인 +92억 순매수, 기관 +6억 순매수 — 운송장비·부품(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>외국인 +10억 순매수, 기관 +2억 순매수, 대차잔고 -310억 감소 — IT 서비스(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>아시아나항공</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="B72" s="35" t="inlineStr">
@@ -2742,42 +2823,42 @@
         </is>
       </c>
       <c r="C72" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="31" t="inlineStr"/>
       <c r="E72" s="31" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="H72" s="35" t="inlineStr">
         <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="I72" s="39" t="n">
-        <v>2</v>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="I72" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="J72" s="31" t="inlineStr"/>
       <c r="K72" s="31" t="inlineStr"/>
     </row>
-    <row r="73" ht="31" customHeight="1" s="15">
+    <row r="73" ht="44.5" customHeight="1" s="15">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>외국인 +3억 순매수, 기관 +2억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>기관 +41억 순매수, 대차잔고 -38억 감소 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
-          <t>외국인 +22억 순매수, 기관 +74억 순매수 — 금속(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="31" customHeight="1" s="15">
+          <t>외국인 +6억 순매수, 기관 +1억 순매수, 대차잔고 -13억 감소 — IT 서비스(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>진에어</t>
+          <t>아시아나항공</t>
         </is>
       </c>
       <c r="B74" s="35" t="inlineStr">
@@ -2786,46 +2867,46 @@
         </is>
       </c>
       <c r="C74" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" s="31" t="inlineStr"/>
       <c r="E74" s="31" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
-        </is>
-      </c>
-      <c r="H74" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="I74" s="39" t="n">
-        <v>2</v>
+          <t>펄어비스</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="I74" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="J74" s="31" t="inlineStr"/>
       <c r="K74" s="31" t="inlineStr"/>
     </row>
-    <row r="75" ht="31" customHeight="1" s="15">
+    <row r="75" ht="44.5" customHeight="1" s="15">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>외국인 +1억 순매수, 기관 +1억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
+          <t>외국인 +3억 순매수, 기관 +2억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
         </is>
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>외국인 +76억 순매수, 기관 +4억 순매수 — 운송장비·부품(수급유입) 섹터 초기 유입형 상방 관찰</t>
+          <t>외국인 +5억 순매수, 기관 +0억 순매수, 대차잔고 -38억 감소 — IT 서비스(수급유입) 섹터 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
     <row r="76"/>
     <row r="77">
-      <c r="A77" s="41" t="inlineStr">
+      <c r="A77" s="39" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G77" s="42" t="inlineStr">
+      <c r="G77" s="40" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -2839,7 +2920,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H78" s="35" t="inlineStr">
@@ -2847,7 +2928,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I78" s="43" t="n">
+      <c r="I78" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J78" s="31" t="inlineStr"/>
@@ -2856,14 +2937,14 @@
     <row r="79" ht="44.5" customHeight="1" s="15">
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>외국인 -20,586억 순매도, 기관 -4,571억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -34억 순매도, 기관 -55억 순매도, 대차잔고 +126억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="H80" s="35" t="inlineStr">
@@ -2871,8 +2952,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I80" s="43" t="n">
-        <v>-3</v>
+      <c r="I80" s="41" t="n">
+        <v>-2</v>
       </c>
       <c r="J80" s="31" t="inlineStr"/>
       <c r="K80" s="31" t="inlineStr"/>
@@ -2880,14 +2961,14 @@
     <row r="81" ht="44.5" customHeight="1" s="15">
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>외국인 -8,440억 순매도, 기관 -4,451억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -23,962억 순매도, 기관 -6,139억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H82" s="35" t="inlineStr">
@@ -2895,8 +2976,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I82" s="43" t="n">
-        <v>-3</v>
+      <c r="I82" s="41" t="n">
+        <v>-2</v>
       </c>
       <c r="J82" s="31" t="inlineStr"/>
       <c r="K82" s="31" t="inlineStr"/>
@@ -2904,23 +2985,23 @@
     <row r="83" ht="44.5" customHeight="1" s="15">
       <c r="G83" s="17" t="inlineStr">
         <is>
-          <t>외국인 -1,317억 순매도, 기관 -696억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -10,512억 순매도, 기관 -7,154억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="H84" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="I84" s="43" t="n">
-        <v>-3</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="I84" s="41" t="n">
+        <v>-2</v>
       </c>
       <c r="J84" s="31" t="inlineStr"/>
       <c r="K84" s="31" t="inlineStr"/>
@@ -2928,37 +3009,37 @@
     <row r="85" ht="44.5" customHeight="1" s="15">
       <c r="G85" s="17" t="inlineStr">
         <is>
-          <t>외국인 -599억 순매도, 기관 -1,174억 순매도, 공매도 누적 상위 등재 — 금융(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -1,503억 순매도, 기관 -886억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="H86" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="I86" s="43" t="n">
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="I86" s="41" t="n">
         <v>-2</v>
       </c>
       <c r="J86" s="31" t="inlineStr"/>
       <c r="K86" s="31" t="inlineStr"/>
     </row>
-    <row r="87" ht="31" customHeight="1" s="15">
+    <row r="87" ht="44.5" customHeight="1" s="15">
       <c r="G87" s="17" t="inlineStr">
         <is>
-          <t>외국인 -234억 순매도, 기관 -140억 순매도 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+          <t>외국인 -941억 순매도, 기관 -1,304억 순매도, 공매도 누적 상위 등재 — 금융(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
     <row r="88"/>
     <row r="89" ht="31" customHeight="1" s="15">
-      <c r="A89" s="44" t="inlineStr">
+      <c r="A89" s="42" t="inlineStr">
         <is>
           <t>현재 확보된 주간 브리핑 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 주간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -3001,28 +3082,28 @@
     <row r="93" ht="15" customHeight="1" s="15">
       <c r="A93" s="17" t="inlineStr">
         <is>
-          <t>- 코스피는 6684.37p로 전일 대비 3.26% 급락했고, 코스닥 역시 1.69% 하락하며 투자 심리가 크게 위축됨.</t>
+          <t>- 코스피는 외국인의 3.3조 원 규모 매도세가 쏟아지며 전일 대비 3.26% 급락한 6684.37에 마감함.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="15">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서 외국인이 3.3조 원, 기관이 1.2조 원을 순매도하며 지수 하락을 주도함.</t>
+          <t>- 코스닥 역시 투자 심리 위축으로 1.69% 하락하며 동반 약세를 보임.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="15">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t>- 개인 투자자가 3.0조 원을 순매수하며 방어에 나섰으나 지수 하락폭을 막기에는 역부족이었음.</t>
+          <t>- 미국발 'AI 속도조절론'이 부각되면서 전기·전자 섹터에 외국인 매물이 집중되어 지수 하락을 주도함.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="15">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>- 미국발 'AI 속도조절론'이 부각되면서 전기·전자 섹터에 외국인 매물이 집중된 것이 지수 하락의 핵심 원인으로 작용함.</t>
+          <t>- 반면 방산 및 조선 섹터는 연이은 수주 계약 성공으로 상대적 견조함을 유지함.</t>
         </is>
       </c>
     </row>
@@ -3051,96 +3132,124 @@
     <row r="99" ht="15" customHeight="1" s="15">
       <c r="A99" s="17" t="inlineStr">
         <is>
-          <t>- 전기·전자 섹터는 AI 인프라 수요 우려로 외국인 매물이 집중되며 -4.78% 급락함.</t>
+          <t>- 전기·전자 섹터는 AI 관련 우려로 외국인 매물이 집중되며 급락세 지속.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="15">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>- 운송·창고 섹터는 지정학적 리스크에 따른 해운 운임 상승 기대감으로 +1.15% 상승하며 견조한 흐름을 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="17" t="inlineStr">
-        <is>
-          <t>- 오락·문화 섹터는 글로벌 IP 파워 기대감으로 +1.2% 상승하며 시장 약세 속 방어적 성격을 나타냄.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102"/>
+          <t>- 운송·창고 및 오락·문화 섹터는 개별 이슈와 수급 유입으로 방어적 흐름을 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>주간 촉매 타임라인</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr"/>
+      <c r="D102" s="3" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr"/>
+      <c r="F102" s="3" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="18" t="inlineStr">
+        <is>
+          <t>등락률 = 주간 누적</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr"/>
+    </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>주간 촉매 타임라인</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr"/>
-      <c r="D103" s="3" t="inlineStr"/>
-      <c r="E103" s="3" t="inlineStr"/>
-      <c r="F103" s="3" t="inlineStr"/>
-      <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="18" t="inlineStr">
-        <is>
-          <t>등락률 = 주간 누적</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="31" customHeight="1" s="15">
+    <row r="104" ht="31" customHeight="1" s="15">
+      <c r="A104" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>인피니트헬스케어</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D104" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F104" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>654억 원 규모의 대규모 현금배당 계획 발표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="15">
       <c r="A105" s="31" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>인피니트헬스케어</t>
+      <c r="B105" s="31" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="C105" s="31" t="inlineStr">
@@ -3150,7 +3259,7 @@
       </c>
       <c r="D105" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -3159,33 +3268,33 @@
         </is>
       </c>
       <c r="F105" s="28" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="G105" s="17" t="inlineStr">
         <is>
-          <t>654억 원 규모의 대규모 현금배당 계획 발표.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="15">
+          <t>차세대 광통신 기술 검증 및 양자통신 클러스터 참여.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="31" customHeight="1" s="15">
       <c r="A106" s="31" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B106" s="31" t="inlineStr">
-        <is>
-          <t>한국첨단소재</t>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C106" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -3194,23 +3303,23 @@
         </is>
       </c>
       <c r="F106" s="28" t="n">
-        <v>29.9</v>
+        <v>5.4</v>
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 기술 검증 및 양자통신 클러스터 참여.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="31" customHeight="1" s="15">
+          <t>K9 자주포 및 천무 등 연이은 수출 계약 성공.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="15">
       <c r="A107" s="31" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B107" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
+      <c r="B107" s="31" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
@@ -3229,11 +3338,11 @@
         </is>
       </c>
       <c r="F107" s="28" t="n">
-        <v>4.56</v>
+        <v>3.27</v>
       </c>
       <c r="G107" s="17" t="inlineStr">
         <is>
-          <t>K9 자주포 및 천무 등 연이은 수출 계약 성공.</t>
+          <t>LNG선 4척 추가 수주를 통한 신규 수주 물량 확보.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3354,7 @@
       </c>
       <c r="B108" s="31" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>영풍</t>
         </is>
       </c>
       <c r="C108" s="31" t="inlineStr">
@@ -3255,7 +3364,7 @@
       </c>
       <c r="D108" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>금속</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -3264,103 +3373,75 @@
         </is>
       </c>
       <c r="F108" s="28" t="n">
-        <v>2.57</v>
+        <v>0.3</v>
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>LNG선 4척 추가 수주를 통한 신규 수주 물량 확보.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="15">
-      <c r="A109" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B109" s="31" t="inlineStr">
-        <is>
-          <t>영풍</t>
-        </is>
-      </c>
-      <c r="C109" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D109" s="35" t="inlineStr">
-        <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="E109" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F109" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G109" s="17" t="inlineStr">
-        <is>
           <t>계열사의 북미 빅테크향 고다층 인쇄회로기판 공급 계약.</t>
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr"/>
-      <c r="D111" s="3" t="inlineStr"/>
-      <c r="E111" s="3" t="inlineStr"/>
-      <c r="F111" s="3" t="inlineStr"/>
-      <c r="G111" s="3" t="inlineStr"/>
-      <c r="H111" s="3" t="inlineStr"/>
-      <c r="I111" s="3" t="inlineStr"/>
-      <c r="J111" s="3" t="inlineStr"/>
-      <c r="K111" s="3" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr"/>
+      <c r="E110" s="3" t="inlineStr"/>
+      <c r="F110" s="3" t="inlineStr"/>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="15">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체 섹터 외국인 매도 진정 시 기술적 반등 전개</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="15">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 섹터 외국인 매도세 진정 시 기술적 반등 전개</t>
+          <t>- AI 속도조절론 지속에 따른 외국인 추가 이탈 시 하방 압력 확대</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="15">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>- AI 속도조절론 지속 및 외국인 매도세 유지 시 추가 하방 압력</t>
+          <t>- 외국인의 반도체 섹터 순매수 전환 여부</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="15">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 전기·전자 섹터 순매수 전환 여부</t>
+          <t>- FOMC 기준금리 결정</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="15">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>- 무역수지 및 수출입 확정치</t>
+          <t>- 무역수지</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="15">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>- FOMC 기준금리 결정</t>
+          <t>- 미국 소매판매</t>
         </is>
       </c>
     </row>
@@ -3384,6 +3465,7 @@
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A78:E78"/>
+    <mergeCell ref="G103:K103"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A99:K99"/>
     <mergeCell ref="A75:E75"/>
@@ -3392,7 +3474,6 @@
     <mergeCell ref="G87:K87"/>
     <mergeCell ref="A89:K89"/>
     <mergeCell ref="G83:K83"/>
-    <mergeCell ref="A101:K101"/>
     <mergeCell ref="G108:K108"/>
     <mergeCell ref="A95:K95"/>
     <mergeCell ref="A71:E71"/>
@@ -3407,7 +3488,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="A100:K100"/>
     <mergeCell ref="A96:K96"/>
-    <mergeCell ref="G109:K109"/>
     <mergeCell ref="G85:K85"/>
     <mergeCell ref="A112:K112"/>
     <mergeCell ref="G32:K32"/>
@@ -3417,6 +3497,7 @@
     <mergeCell ref="G106:K106"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A111:K111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3428,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18.5" customWidth="1" style="15" min="1" max="1"/>
@@ -3507,62 +3588,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="43" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="43" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="43" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="43" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="43" t="inlineStr">
         <is>
           <t>주간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="43" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -3584,32 +3665,32 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
-        <v>87</v>
-      </c>
-      <c r="E6" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="46" t="n">
-        <v>86</v>
-      </c>
-      <c r="G6" s="48" t="n">
-        <v>-86</v>
-      </c>
-      <c r="H6" s="49" t="n">
+      <c r="D6" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="E6" s="44" t="n">
+        <v>34</v>
+      </c>
+      <c r="F6" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="G6" s="45" t="n">
+        <v>-76</v>
+      </c>
+      <c r="H6" s="46" t="n">
         <v>303.7</v>
       </c>
-      <c r="I6" s="49" t="n">
-        <v>6617.4</v>
-      </c>
-      <c r="J6" s="50" t="n">
-        <v>-331.9</v>
-      </c>
-      <c r="K6" s="51" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="L6" s="52" t="n">
-        <v>-7.58</v>
+      <c r="I6" s="46" t="n">
+        <v>6793.5</v>
+      </c>
+      <c r="J6" s="47" t="n">
+        <v>46</v>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L6" s="49" t="n">
+        <v>-7.34</v>
       </c>
     </row>
     <row r="7">
@@ -3628,32 +3709,32 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" s="48" t="n">
-        <v>-104</v>
-      </c>
-      <c r="F7" s="46" t="n">
-        <v>158</v>
-      </c>
-      <c r="G7" s="48" t="n">
-        <v>-52</v>
-      </c>
-      <c r="H7" s="49" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="I7" s="49" t="n">
-        <v>6883</v>
-      </c>
-      <c r="J7" s="50" t="n">
-        <v>-573.8</v>
-      </c>
-      <c r="K7" s="51" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="L7" s="53" t="n">
-        <v>-1.92</v>
+      <c r="D7" s="44" t="n">
+        <v>59</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>-53</v>
+      </c>
+      <c r="F7" s="44" t="n">
+        <v>112</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <v>-58</v>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="I7" s="46" t="n">
+        <v>7357.9</v>
+      </c>
+      <c r="J7" s="47" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L7" s="50" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="8">
@@ -3672,32 +3753,32 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D8" s="46" t="n">
-        <v>83</v>
-      </c>
-      <c r="E8" s="46" t="n">
-        <v>127</v>
-      </c>
-      <c r="F8" s="48" t="n">
-        <v>-44</v>
-      </c>
-      <c r="G8" s="48" t="n">
-        <v>-77</v>
-      </c>
-      <c r="H8" s="49" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="I8" s="49" t="n">
-        <v>6878.3</v>
-      </c>
-      <c r="J8" s="50" t="n">
-        <v>-620.4</v>
-      </c>
-      <c r="K8" s="51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L8" s="53" t="n">
-        <v>-1.93</v>
+      <c r="D8" s="44" t="n">
+        <v>107</v>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>185</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>-78</v>
+      </c>
+      <c r="G8" s="45" t="n">
+        <v>-98</v>
+      </c>
+      <c r="H8" s="46" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>7122.1</v>
+      </c>
+      <c r="J8" s="47" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L8" s="50" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="9">
@@ -3716,116 +3797,120 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="44" t="n">
         <v>158</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="44" t="n">
         <v>78</v>
       </c>
-      <c r="G9" s="48" t="n">
-        <v>-159</v>
-      </c>
-      <c r="H9" s="49" t="n">
+      <c r="G9" s="45" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H9" s="46" t="n">
         <v>22.6</v>
       </c>
-      <c r="I9" s="49" t="n">
-        <v>1741.8</v>
-      </c>
-      <c r="J9" s="54" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="K9" s="51" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L9" s="55" t="n">
-        <v>-4.7</v>
+      <c r="I9" s="46" t="n">
+        <v>1755.7</v>
+      </c>
+      <c r="J9" s="47" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L9" s="49" t="n">
+        <v>-5.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>31</v>
-      </c>
-      <c r="E10" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" s="48" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H10" s="49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I10" s="49" t="n">
-        <v>224.4</v>
-      </c>
-      <c r="J10" s="54" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="K10" s="51" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L10" s="55" t="n">
-        <v>-4.55</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" s="45" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F10" s="44" t="n">
+        <v>58</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>940.4</v>
+      </c>
+      <c r="J10" s="47" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="L10" s="49" t="n">
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>38</v>
-      </c>
-      <c r="E11" s="48" t="n">
-        <v>-25</v>
-      </c>
-      <c r="F11" s="46" t="n">
-        <v>63</v>
-      </c>
-      <c r="G11" s="48" t="n">
-        <v>-38</v>
-      </c>
-      <c r="H11" s="49" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="I11" s="49" t="inlineStr"/>
-      <c r="J11" s="56" t="inlineStr"/>
-      <c r="K11" s="51" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="L11" s="52" t="n">
-        <v>-8.800000000000001</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" s="45" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H11" s="46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="J11" s="47" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L11" s="49" t="n">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="12">
@@ -3844,38 +3929,38 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="46" t="n">
+      <c r="D12" s="45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="48" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H12" s="49" t="n">
+      <c r="H12" s="46" t="n">
         <v>12.4</v>
       </c>
-      <c r="I12" s="49" t="n">
-        <v>1222.1</v>
-      </c>
-      <c r="J12" s="50" t="n">
-        <v>-68.2</v>
-      </c>
-      <c r="K12" s="51" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="L12" s="52" t="n">
-        <v>-7.47</v>
+      <c r="I12" s="46" t="n">
+        <v>1225.3</v>
+      </c>
+      <c r="J12" s="51" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L12" s="49" t="n">
+        <v>-7.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -3885,119 +3970,119 @@
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="n">
-        <v>27</v>
-      </c>
-      <c r="E13" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="F13" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="G13" s="48" t="n">
-        <v>-27</v>
-      </c>
-      <c r="H13" s="49" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I13" s="49" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="J13" s="50" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="K13" s="57" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="L13" s="52" t="n">
-        <v>-7.58</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>-34</v>
+      </c>
+      <c r="F13" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="G13" s="45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>1228.9</v>
+      </c>
+      <c r="J13" s="47" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L13" s="49" t="n">
+        <v>-9.09</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>팬오션</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>리파인</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr"/>
+      <c r="D14" s="45" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E14" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>-29</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I14" s="46" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="J14" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L14" s="50" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>BGF리테일</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="48" t="n">
-        <v>-34</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <v>37</v>
-      </c>
-      <c r="G14" s="48" t="n">
-        <v>-4</v>
-      </c>
-      <c r="H14" s="49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I14" s="49" t="n">
-        <v>1187.8</v>
-      </c>
-      <c r="J14" s="50" t="n">
-        <v>-51.8</v>
-      </c>
-      <c r="K14" s="51" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="L14" s="52" t="n">
-        <v>-8.73</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>리파인</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr"/>
-      <c r="D15" s="48" t="n">
-        <v>-17</v>
-      </c>
-      <c r="E15" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="48" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G15" s="48" t="n">
-        <v>-32</v>
-      </c>
-      <c r="H15" s="49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I15" s="49" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="J15" s="50" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="K15" s="51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L15" s="53" t="n">
-        <v>-0.29</v>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F15" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I15" s="46" t="n">
+        <v>1121.9</v>
+      </c>
+      <c r="J15" s="47" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="K15" s="52" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="L15" s="49" t="n">
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4012,28 +4097,32 @@
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr"/>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="E16" s="48" t="n">
+      <c r="E16" s="45" t="n">
         <v>-2</v>
       </c>
-      <c r="F16" s="46" t="n">
+      <c r="F16" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="48" t="n">
+      <c r="G16" s="45" t="n">
         <v>-7</v>
       </c>
-      <c r="H16" s="49" t="n">
+      <c r="H16" s="46" t="n">
         <v>0.9</v>
       </c>
-      <c r="I16" s="49" t="inlineStr"/>
-      <c r="J16" s="56" t="inlineStr"/>
-      <c r="K16" s="51" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="L16" s="55" t="n">
-        <v>-4.76</v>
+      <c r="I16" s="46" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J16" s="47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K16" s="48" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="L16" s="49" t="n">
+        <v>-5.52</v>
       </c>
     </row>
     <row r="17">
@@ -4048,32 +4137,36 @@
         </is>
       </c>
       <c r="C17" s="35" t="inlineStr"/>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="44" t="n">
         <v>19</v>
       </c>
-      <c r="E17" s="48" t="n">
+      <c r="E17" s="45" t="n">
         <v>-1</v>
       </c>
-      <c r="F17" s="46" t="n">
+      <c r="F17" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="G17" s="48" t="n">
+      <c r="G17" s="45" t="n">
         <v>-37</v>
       </c>
-      <c r="H17" s="49" t="inlineStr"/>
-      <c r="I17" s="49" t="inlineStr"/>
-      <c r="J17" s="56" t="inlineStr"/>
-      <c r="K17" s="51" t="n">
+      <c r="H17" s="46" t="inlineStr"/>
+      <c r="I17" s="46" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J17" s="47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K17" s="48" t="n">
         <v>30</v>
       </c>
-      <c r="L17" s="53" t="n">
+      <c r="L17" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>IPARK현대산업개발</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
@@ -4083,121 +4176,125 @@
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="48" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F18" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="48" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H18" s="49" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I18" s="49" t="n">
-        <v>1075.2</v>
-      </c>
-      <c r="J18" s="54" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="K18" s="57" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="L18" s="52" t="n">
-        <v>-7.33</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="45" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G18" s="45" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>470</v>
+      </c>
+      <c r="J18" s="51" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="K18" s="52" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="L18" s="53" t="n">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>시선AI</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D19" s="48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E19" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="48" t="n">
-        <v>-8</v>
-      </c>
-      <c r="G19" s="48" t="n">
-        <v>-6</v>
-      </c>
-      <c r="H19" s="49" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I19" s="49" t="n">
-        <v>464.4</v>
-      </c>
-      <c r="J19" s="54" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="K19" s="57" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="L19" s="55" t="n">
-        <v>-3.3</v>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr"/>
+      <c r="D19" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H19" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="46" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J19" s="47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" s="48" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L19" s="49" t="n">
+        <v>-6.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>시선AI</t>
+          <t>빙그레</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr"/>
-      <c r="D20" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="48" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H20" s="49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I20" s="49" t="inlineStr"/>
-      <c r="J20" s="56" t="inlineStr"/>
-      <c r="K20" s="51" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="L20" s="52" t="n">
-        <v>-6.56</v>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E20" s="45" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G20" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" s="46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" s="46" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="J20" s="51" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="K20" s="52" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="L20" s="49" t="n">
+        <v>-9.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>빙그레</t>
+          <t>롯데웰푸드</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
@@ -4210,38 +4307,38 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="48" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G21" s="48" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H21" s="49" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I21" s="49" t="n">
-        <v>323.3</v>
-      </c>
-      <c r="J21" s="50" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="K21" s="57" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="L21" s="52" t="n">
-        <v>-9.710000000000001</v>
+      <c r="D21" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="45" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G21" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I21" s="46" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="J21" s="51" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="K21" s="48" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L21" s="49" t="n">
+        <v>-9.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>롯데웰푸드</t>
+          <t>코리안리</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
@@ -4251,41 +4348,41 @@
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="D22" s="48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E22" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" s="48" t="n">
-        <v>-11</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" s="49" t="n">
-        <v>365.3</v>
-      </c>
-      <c r="J22" s="54" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K22" s="57" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="L22" s="52" t="n">
-        <v>-9.31</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H22" s="46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>870.4</v>
+      </c>
+      <c r="J22" s="47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K22" s="48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L22" s="53" t="n">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>코리안리</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
@@ -4295,41 +4392,41 @@
       </c>
       <c r="C23" s="35" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D23" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="48" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H23" s="49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I23" s="49" t="n">
-        <v>844.6</v>
-      </c>
-      <c r="J23" s="54" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K23" s="51" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="L23" s="55" t="n">
-        <v>-3.16</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D23" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F23" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="45" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H23" s="46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I23" s="46" t="n">
+        <v>604.8</v>
+      </c>
+      <c r="J23" s="47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="49" t="n">
+        <v>-7.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>KB발해인프라</t>
         </is>
       </c>
       <c r="B24" s="30" t="inlineStr">
@@ -4337,174 +4434,48 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D24" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" s="48" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F24" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" s="48" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H24" s="49" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I24" s="49" t="n">
-        <v>592.2</v>
-      </c>
-      <c r="J24" s="50" t="n">
-        <v>-27.8</v>
-      </c>
-      <c r="K24" s="51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L24" s="52" t="n">
-        <v>-7.06</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>KB발해인프라</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr"/>
-      <c r="D25" s="47" t="n">
+      <c r="C24" s="35" t="inlineStr"/>
+      <c r="D24" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="46" t="n">
+      <c r="E24" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="F25" s="48" t="n">
+      <c r="F24" s="45" t="n">
         <v>-13</v>
       </c>
-      <c r="G25" s="47" t="n">
+      <c r="G24" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="49" t="n">
+      <c r="H24" s="46" t="n">
         <v>0.1</v>
       </c>
-      <c r="I25" s="49" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="J25" s="50" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="K25" s="57" t="n">
+      <c r="I24" s="46" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="J24" s="51" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="K24" s="52" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L25" s="52" t="n">
+      <c r="L24" s="49" t="n">
         <v>-7.66</v>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>S-Oil우</t>
-        </is>
-      </c>
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D26" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="48" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F26" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I26" s="49" t="n">
-        <v>175.6</v>
-      </c>
-      <c r="J26" s="54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K26" s="51" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="L26" s="52" t="n">
-        <v>-7.82</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>방림</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>섬유·의류</t>
-        </is>
-      </c>
-      <c r="D27" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="49" t="inlineStr"/>
-      <c r="I27" s="49" t="inlineStr"/>
-      <c r="J27" s="56" t="inlineStr"/>
-      <c r="K27" s="51" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="L27" s="55" t="n">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=주간 누적 확정(억원) · 동반 순매수(외인·기관 동일 방향)=합산 굵게</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L27"/>
+  <autoFilter ref="A5:L24"/>
   <mergeCells count="6">
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A29:L29"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="K4:L4"/>
@@ -4520,7 +4491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="15" min="1" max="1"/>
@@ -4566,7 +4537,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr">
+      <c r="E3" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -4576,111 +4547,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="59" t="inlineStr">
+      <c r="N3" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="60" t="inlineStr">
+      <c r="J4" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="61" t="inlineStr">
+      <c r="N4" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="M5" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="45" t="inlineStr">
+      <c r="N5" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="45" t="inlineStr">
+      <c r="O5" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="45" t="inlineStr">
+      <c r="P5" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="45" t="inlineStr">
+      <c r="Q5" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -4700,8 +4671,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D6" s="48" t="n">
-        <v>431</v>
+      <c r="D6" s="45" t="n">
+        <v>528</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>1</v>
@@ -4716,8 +4687,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="62" t="n">
-        <v>-20586</v>
+      <c r="H6" s="59" t="n">
+        <v>-23962</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>1</v>
@@ -4732,7 +4703,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="M6" s="48" t="n">
+      <c r="M6" s="45" t="n">
         <v>275</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -4740,7 +4711,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="P6" s="35" t="inlineStr">
@@ -4748,8 +4719,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="62" t="n">
-        <v>-4571</v>
+      <c r="Q6" s="59" t="n">
+        <v>-7154</v>
       </c>
     </row>
     <row r="7">
@@ -4766,8 +4737,8 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D7" s="48" t="n">
-        <v>349</v>
+      <c r="D7" s="45" t="n">
+        <v>359</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>2</v>
@@ -4782,8 +4753,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="62" t="n">
-        <v>-8440</v>
+      <c r="H7" s="59" t="n">
+        <v>-10512</v>
       </c>
       <c r="J7" s="30" t="n">
         <v>2</v>
@@ -4798,15 +4769,15 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="M7" s="48" t="n">
-        <v>222</v>
+      <c r="M7" s="45" t="n">
+        <v>216</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="P7" s="35" t="inlineStr">
@@ -4814,8 +4785,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="62" t="n">
-        <v>-4451</v>
+      <c r="Q7" s="59" t="n">
+        <v>-6139</v>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1" s="15">
@@ -4824,16 +4795,16 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D8" s="48" t="n">
-        <v>218</v>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>278</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>3</v>
@@ -4848,24 +4819,24 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H8" s="62" t="n">
-        <v>-2038</v>
+      <c r="H8" s="59" t="n">
+        <v>-2095</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K8" s="31" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
-        </is>
-      </c>
-      <c r="L8" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="M8" s="48" t="n">
-        <v>181</v>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="L8" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M8" s="45" t="n">
+        <v>177</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>3</v>
@@ -4880,26 +4851,26 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="Q8" s="62" t="n">
-        <v>-1174</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="Q8" s="59" t="n">
+        <v>-1304</v>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1" s="15">
       <c r="A9" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>GS</t>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="n">
-        <v>188</v>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>197</v>
       </c>
       <c r="E9" s="30" t="n">
         <v>4</v>
@@ -4914,24 +4885,24 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="62" t="n">
-        <v>-1317</v>
+      <c r="H9" s="59" t="n">
+        <v>-1503</v>
       </c>
       <c r="J9" s="30" t="n">
         <v>4</v>
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="L9" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="M9" s="48" t="n">
-        <v>177</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="M9" s="45" t="n">
+        <v>166</v>
       </c>
       <c r="N9" s="30" t="n">
         <v>4</v>
@@ -4946,8 +4917,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q9" s="62" t="n">
-        <v>-696</v>
+      <c r="Q9" s="59" t="n">
+        <v>-886</v>
       </c>
     </row>
     <row r="10" ht="31" customHeight="1" s="15">
@@ -4956,16 +4927,16 @@
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="D10" s="48" t="n">
-        <v>169</v>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>196</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>5</v>
@@ -4980,24 +4951,24 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="H10" s="62" t="n">
-        <v>-599</v>
+      <c r="H10" s="59" t="n">
+        <v>-941</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="K10" s="31" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="L10" s="35" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="M10" s="48" t="n">
-        <v>169</v>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="L10" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="M10" s="45" t="n">
+        <v>166</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>5</v>
@@ -5012,26 +4983,26 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q10" s="62" t="n">
-        <v>-470</v>
-      </c>
-    </row>
-    <row r="11" ht="31" customHeight="1" s="15">
+      <c r="Q10" s="59" t="n">
+        <v>-547</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="D11" s="48" t="n">
-        <v>148</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="n">
+        <v>192</v>
       </c>
       <c r="E11" s="30" t="n">
         <v>6</v>
@@ -5046,8 +5017,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H11" s="62" t="n">
-        <v>-451</v>
+      <c r="H11" s="59" t="n">
+        <v>-637</v>
       </c>
       <c r="J11" s="30" t="n">
         <v>6</v>
@@ -5062,8 +5033,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M11" s="48" t="n">
-        <v>162</v>
+      <c r="M11" s="45" t="n">
+        <v>155</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>6</v>
@@ -5078,8 +5049,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q11" s="62" t="n">
-        <v>-466</v>
+      <c r="Q11" s="59" t="n">
+        <v>-520</v>
       </c>
     </row>
     <row r="12" ht="31" customHeight="1" s="15">
@@ -5088,16 +5059,16 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="D12" s="48" t="n">
-        <v>142</v>
+          <t>하나금융지주</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>185</v>
       </c>
       <c r="E12" s="30" t="n">
         <v>7</v>
@@ -5112,24 +5083,24 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="H12" s="62" t="n">
-        <v>-339</v>
+      <c r="H12" s="59" t="n">
+        <v>-379</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>7</v>
       </c>
       <c r="K12" s="31" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="L12" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M12" s="48" t="n">
-        <v>158</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="M12" s="45" t="n">
+        <v>145</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>7</v>
@@ -5139,31 +5110,31 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P12" s="38" t="inlineStr">
+      <c r="P12" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q12" s="62" t="n">
-        <v>-323</v>
+      <c r="Q12" s="59" t="n">
+        <v>-427</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" s="15">
       <c r="A13" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="n">
-        <v>140</v>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>169</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>8</v>
@@ -5178,58 +5149,58 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="H13" s="62" t="n">
-        <v>-259</v>
+      <c r="H13" s="59" t="n">
+        <v>-297</v>
       </c>
       <c r="J13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="31" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
-        </is>
-      </c>
-      <c r="L13" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="M13" s="48" t="n">
-        <v>149</v>
+          <t>한화엔진</t>
+        </is>
+      </c>
+      <c r="L13" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="M13" s="45" t="n">
+        <v>144</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O13" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="P13" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="Q13" s="62" t="n">
-        <v>-244</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="15">
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="P13" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="Q13" s="59" t="n">
+        <v>-257</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D14" s="48" t="n">
-        <v>127</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>152</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>9</v>
@@ -5244,8 +5215,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H14" s="62" t="n">
-        <v>-234</v>
+      <c r="H14" s="59" t="n">
+        <v>-291</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>9</v>
@@ -5260,24 +5231,24 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="M14" s="48" t="n">
-        <v>149</v>
+      <c r="M14" s="45" t="n">
+        <v>142</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="O14" s="31" t="inlineStr">
-        <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="P14" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="Q14" s="62" t="n">
-        <v>-227</v>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="P14" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="Q14" s="59" t="n">
+        <v>-254</v>
       </c>
     </row>
     <row r="15">
@@ -5286,55 +5257,55 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="n">
-        <v>122</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>134</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>한화엔진</t>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="H15" s="62" t="n">
-        <v>-202</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="H15" s="59" t="n">
+        <v>-272</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>10</v>
       </c>
       <c r="K15" s="31" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="L15" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="M15" s="48" t="n">
-        <v>147</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="M15" s="45" t="n">
+        <v>137</v>
       </c>
       <c r="N15" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O15" s="31" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="P15" s="35" t="inlineStr">
@@ -5342,8 +5313,8 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q15" s="62" t="n">
-        <v>-185</v>
+      <c r="Q15" s="59" t="n">
+        <v>-239</v>
       </c>
     </row>
     <row r="16"/>
@@ -5353,7 +5324,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="E17" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -5363,111 +5334,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="59" t="inlineStr">
+      <c r="N17" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="61" t="inlineStr">
+      <c r="E18" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="60" t="inlineStr">
+      <c r="J18" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="61" t="inlineStr">
+      <c r="N18" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="45" t="inlineStr">
+      <c r="J19" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="45" t="inlineStr">
+      <c r="K19" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="L19" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M19" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="45" t="inlineStr">
+      <c r="N19" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="45" t="inlineStr">
+      <c r="O19" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="45" t="inlineStr">
+      <c r="P19" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="45" t="inlineStr">
+      <c r="Q19" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5487,8 +5458,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D20" s="48" t="n">
-        <v>397</v>
+      <c r="D20" s="45" t="n">
+        <v>482</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>1</v>
@@ -5503,8 +5474,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="62" t="n">
-        <v>-25157</v>
+      <c r="H20" s="59" t="n">
+        <v>-30101</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>1</v>
@@ -5519,8 +5490,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="48" t="n">
-        <v>15259</v>
+      <c r="M20" s="45" t="n">
+        <v>20306</v>
       </c>
       <c r="N20" s="30" t="n">
         <v>1</v>
@@ -5535,8 +5506,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="Q20" s="62" t="n">
-        <v>-393</v>
+      <c r="Q20" s="59" t="n">
+        <v>-478</v>
       </c>
     </row>
     <row r="21" ht="31" customHeight="1" s="15">
@@ -5545,16 +5516,16 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
-        </is>
-      </c>
-      <c r="C21" s="38" t="inlineStr">
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D21" s="48" t="n">
-        <v>285</v>
+      <c r="D21" s="45" t="n">
+        <v>393</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>2</v>
@@ -5569,8 +5540,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="62" t="n">
-        <v>-12891</v>
+      <c r="H21" s="59" t="n">
+        <v>-17666</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>2</v>
@@ -5585,8 +5556,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M21" s="48" t="n">
-        <v>8616</v>
+      <c r="M21" s="45" t="n">
+        <v>13639</v>
       </c>
       <c r="N21" s="30" t="n">
         <v>2</v>
@@ -5596,13 +5567,13 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P21" s="38" t="inlineStr">
+      <c r="P21" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q21" s="62" t="n">
-        <v>-295</v>
+      <c r="Q21" s="59" t="n">
+        <v>-422</v>
       </c>
     </row>
     <row r="22" ht="31" customHeight="1" s="15">
@@ -5611,23 +5582,23 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
-        </is>
-      </c>
-      <c r="C22" s="38" t="inlineStr">
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D22" s="48" t="n">
-        <v>267</v>
+      <c r="D22" s="45" t="n">
+        <v>335</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F22" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -5635,15 +5606,15 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H22" s="62" t="n">
-        <v>-2027</v>
+      <c r="H22" s="59" t="n">
+        <v>-2389</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K22" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="L22" s="35" t="inlineStr">
@@ -5651,8 +5622,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M22" s="48" t="n">
-        <v>2006</v>
+      <c r="M22" s="45" t="n">
+        <v>2354</v>
       </c>
       <c r="N22" s="30" t="n">
         <v>3</v>
@@ -5662,13 +5633,13 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="P22" s="38" t="inlineStr">
+      <c r="P22" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q22" s="62" t="n">
-        <v>-287</v>
+      <c r="Q22" s="59" t="n">
+        <v>-335</v>
       </c>
     </row>
     <row r="23" ht="31" customHeight="1" s="15">
@@ -5685,40 +5656,40 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="D23" s="48" t="n">
-        <v>224</v>
+      <c r="D23" s="45" t="n">
+        <v>266</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="H23" s="62" t="n">
-        <v>-2013</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H23" s="59" t="n">
+        <v>-2246</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>4</v>
       </c>
       <c r="K23" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="L23" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="M23" s="48" t="n">
-        <v>1988</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="M23" s="45" t="n">
+        <v>2197</v>
       </c>
       <c r="N23" s="30" t="n">
         <v>4</v>
@@ -5733,8 +5704,8 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="Q23" s="62" t="n">
-        <v>-220</v>
+      <c r="Q23" s="59" t="n">
+        <v>-262</v>
       </c>
     </row>
     <row r="24">
@@ -5751,40 +5722,40 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D24" s="48" t="n">
-        <v>221</v>
+      <c r="D24" s="45" t="n">
+        <v>228</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F24" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="H24" s="62" t="n">
-        <v>-1773</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H24" s="59" t="n">
+        <v>-2085</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>5</v>
       </c>
       <c r="K24" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="L24" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M24" s="48" t="n">
-        <v>1726</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M24" s="45" t="n">
+        <v>2057</v>
       </c>
       <c r="N24" s="30" t="n">
         <v>5</v>
@@ -5799,8 +5770,8 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="Q24" s="62" t="n">
-        <v>-218</v>
+      <c r="Q24" s="59" t="n">
+        <v>-223</v>
       </c>
     </row>
     <row r="25">
@@ -5817,7 +5788,7 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D25" s="48" t="n">
+      <c r="D25" s="45" t="n">
         <v>158</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -5833,8 +5804,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H25" s="62" t="n">
-        <v>-921</v>
+      <c r="H25" s="59" t="n">
+        <v>-1184</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>6</v>
@@ -5849,8 +5820,8 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M25" s="48" t="n">
-        <v>947</v>
+      <c r="M25" s="45" t="n">
+        <v>1221</v>
       </c>
       <c r="N25" s="30" t="n">
         <v>6</v>
@@ -5865,8 +5836,8 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="Q25" s="62" t="n">
-        <v>-159</v>
+      <c r="Q25" s="59" t="n">
+        <v>-158</v>
       </c>
     </row>
     <row r="26">
@@ -5883,8 +5854,8 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="D26" s="48" t="n">
-        <v>120</v>
+      <c r="D26" s="45" t="n">
+        <v>133</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>7</v>
@@ -5899,8 +5870,8 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="H26" s="62" t="n">
-        <v>-380</v>
+      <c r="H26" s="59" t="n">
+        <v>-526</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>7</v>
@@ -5915,8 +5886,8 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="M26" s="48" t="n">
-        <v>387</v>
+      <c r="M26" s="45" t="n">
+        <v>533</v>
       </c>
       <c r="N26" s="30" t="n">
         <v>7</v>
@@ -5931,8 +5902,8 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="Q26" s="62" t="n">
-        <v>-121</v>
+      <c r="Q26" s="59" t="n">
+        <v>-136</v>
       </c>
     </row>
     <row r="27">
@@ -5949,8 +5920,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D27" s="48" t="n">
-        <v>117</v>
+      <c r="D27" s="45" t="n">
+        <v>126</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>8</v>
@@ -5965,8 +5936,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H27" s="62" t="n">
-        <v>-374</v>
+      <c r="H27" s="59" t="n">
+        <v>-461</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>8</v>
@@ -5981,8 +5952,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M27" s="48" t="n">
-        <v>340</v>
+      <c r="M27" s="45" t="n">
+        <v>424</v>
       </c>
       <c r="N27" s="30" t="n">
         <v>8</v>
@@ -5997,17 +5968,17 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="Q27" s="62" t="n">
-        <v>-118</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="Q27" s="59" t="n">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="28" ht="31" customHeight="1" s="15">
       <c r="A28" s="30" t="n">
         <v>9</v>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C28" s="35" t="inlineStr">
@@ -6015,8 +5986,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="48" t="n">
-        <v>107</v>
+      <c r="D28" s="45" t="n">
+        <v>123</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>9</v>
@@ -6031,31 +6002,31 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="H28" s="62" t="n">
-        <v>-330</v>
+      <c r="H28" s="59" t="n">
+        <v>-395</v>
       </c>
       <c r="J28" s="30" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
-        </is>
-      </c>
-      <c r="L28" s="35" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="M28" s="48" t="n">
-        <v>327</v>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="L28" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="M28" s="45" t="n">
+        <v>390</v>
       </c>
       <c r="N28" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O28" s="31" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="P28" s="35" t="inlineStr">
@@ -6063,11 +6034,11 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q28" s="62" t="n">
-        <v>-101</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="Q28" s="59" t="n">
+        <v>-124</v>
+      </c>
+    </row>
+    <row r="29" ht="31" customHeight="1" s="15">
       <c r="A29" s="30" t="n">
         <v>10</v>
       </c>
@@ -6081,56 +6052,56 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D29" s="48" t="n">
-        <v>105</v>
+      <c r="D29" s="45" t="n">
+        <v>120</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F29" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="G29" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="H29" s="62" t="n">
-        <v>-248</v>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="G29" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="H29" s="59" t="n">
+        <v>-381</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="L29" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="M29" s="48" t="n">
-        <v>252</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="M29" s="45" t="n">
+        <v>386</v>
       </c>
       <c r="N29" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O29" s="31" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
-        </is>
-      </c>
-      <c r="P29" s="35" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="Q29" s="62" t="n">
-        <v>-89</v>
+          <t>한국항공우주</t>
+        </is>
+      </c>
+      <c r="P29" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="Q29" s="59" t="n">
+        <v>-103</v>
       </c>
     </row>
     <row r="30"/>
@@ -6140,7 +6111,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="59" t="inlineStr">
+      <c r="E31" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -6150,111 +6121,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="59" t="inlineStr">
+      <c r="N31" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="61" t="inlineStr">
+      <c r="E32" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="60" t="inlineStr">
+      <c r="J32" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="61" t="inlineStr">
+      <c r="N32" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr">
+      <c r="E33" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="45" t="inlineStr">
+      <c r="F33" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="45" t="inlineStr">
+      <c r="G33" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="45" t="inlineStr">
+      <c r="H33" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="45" t="inlineStr">
+      <c r="J33" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="K33" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M33" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N33" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O33" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="45" t="inlineStr">
+      <c r="P33" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="45" t="inlineStr">
+      <c r="Q33" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6274,7 +6245,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="48" t="n">
+      <c r="D34" s="45" t="n">
         <v>61</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -6290,8 +6261,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H34" s="62" t="n">
-        <v>-1754</v>
+      <c r="H34" s="59" t="n">
+        <v>-3649</v>
       </c>
       <c r="J34" s="30" t="n">
         <v>1</v>
@@ -6301,12 +6272,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L34" s="38" t="inlineStr">
+      <c r="L34" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M34" s="48" t="n">
+      <c r="M34" s="45" t="n">
         <v>260</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -6322,8 +6293,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="62" t="n">
-        <v>-3511</v>
+      <c r="Q34" s="59" t="n">
+        <v>-4124</v>
       </c>
     </row>
     <row r="35">
@@ -6332,16 +6303,16 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C35" s="35" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D35" s="48" t="n">
-        <v>29</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D35" s="45" t="n">
+        <v>22</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>2</v>
@@ -6356,8 +6327,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H35" s="62" t="n">
-        <v>-591</v>
+      <c r="H35" s="59" t="n">
+        <v>-1548</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>2</v>
@@ -6372,7 +6343,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="M35" s="48" t="n">
+      <c r="M35" s="45" t="n">
         <v>245</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -6388,8 +6359,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q35" s="62" t="n">
-        <v>-2152</v>
+      <c r="Q35" s="59" t="n">
+        <v>-2961</v>
       </c>
     </row>
     <row r="36">
@@ -6398,32 +6369,32 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="C36" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D36" s="48" t="n">
-        <v>22</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D36" s="45" t="n">
+        <v>20</v>
       </c>
       <c r="E36" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F36" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="H36" s="62" t="n">
-        <v>-245</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H36" s="59" t="n">
+        <v>-363</v>
       </c>
       <c r="J36" s="30" t="n">
         <v>3</v>
@@ -6438,8 +6409,8 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="M36" s="48" t="n">
-        <v>200</v>
+      <c r="M36" s="45" t="n">
+        <v>202</v>
       </c>
       <c r="N36" s="30" t="n">
         <v>3</v>
@@ -6454,7 +6425,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q36" s="62" t="n">
+      <c r="Q36" s="59" t="n">
         <v>-457</v>
       </c>
     </row>
@@ -6464,32 +6435,32 @@
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C37" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D37" s="48" t="n">
-        <v>19</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D37" s="45" t="n">
+        <v>12</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>4</v>
       </c>
       <c r="F37" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="H37" s="62" t="n">
-        <v>-237</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="H37" s="59" t="n">
+        <v>-315</v>
       </c>
       <c r="J37" s="30" t="n">
         <v>4</v>
@@ -6504,7 +6475,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M37" s="48" t="n">
+      <c r="M37" s="45" t="n">
         <v>147</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -6520,8 +6491,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="Q37" s="62" t="n">
-        <v>-239</v>
+      <c r="Q37" s="59" t="n">
+        <v>-262</v>
       </c>
     </row>
     <row r="38">
@@ -6530,16 +6501,16 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D38" s="48" t="n">
-        <v>15</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D38" s="45" t="n">
+        <v>8</v>
       </c>
       <c r="E38" s="30" t="n">
         <v>5</v>
@@ -6554,8 +6525,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="H38" s="62" t="n">
-        <v>-167</v>
+      <c r="H38" s="59" t="n">
+        <v>-274</v>
       </c>
       <c r="J38" s="30" t="n">
         <v>5</v>
@@ -6570,7 +6541,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M38" s="48" t="n">
+      <c r="M38" s="45" t="n">
         <v>129</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -6586,42 +6557,42 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q38" s="62" t="n">
-        <v>-232</v>
-      </c>
-    </row>
-    <row r="39" ht="31" customHeight="1" s="15">
+      <c r="Q38" s="59" t="n">
+        <v>-239</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="30" t="n">
         <v>6</v>
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C39" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="D39" s="48" t="n">
-        <v>14</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D39" s="45" t="n">
+        <v>6</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F39" s="31" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="H39" s="62" t="n">
-        <v>-149</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H39" s="59" t="n">
+        <v>-184</v>
       </c>
       <c r="J39" s="30" t="n">
         <v>6</v>
@@ -6636,7 +6607,7 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="M39" s="48" t="n">
+      <c r="M39" s="45" t="n">
         <v>126</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -6644,33 +6615,33 @@
       </c>
       <c r="O39" s="31" t="inlineStr">
         <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="P39" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="Q39" s="62" t="n">
-        <v>-194</v>
-      </c>
-    </row>
-    <row r="40">
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="P39" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="Q39" s="59" t="n">
+        <v>-234</v>
+      </c>
+    </row>
+    <row r="40" ht="31" customHeight="1" s="15">
       <c r="A40" s="30" t="n">
         <v>7</v>
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C40" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D40" s="48" t="n">
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="n">
         <v>6</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -6678,16 +6649,16 @@
       </c>
       <c r="F40" s="31" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="H40" s="62" t="n">
-        <v>-141</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H40" s="59" t="n">
+        <v>-165</v>
       </c>
       <c r="J40" s="30" t="n">
         <v>7</v>
@@ -6702,7 +6673,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M40" s="48" t="n">
+      <c r="M40" s="45" t="n">
         <v>121</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -6710,16 +6681,16 @@
       </c>
       <c r="O40" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="P40" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="Q40" s="62" t="n">
-        <v>-169</v>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P40" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="Q40" s="59" t="n">
+        <v>-195</v>
       </c>
     </row>
     <row r="41">
@@ -6728,23 +6699,23 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C41" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D41" s="48" t="n">
-        <v>6</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D41" s="45" t="n">
+        <v>4</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>8</v>
       </c>
       <c r="F41" s="31" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -6752,8 +6723,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="H41" s="62" t="n">
-        <v>-131</v>
+      <c r="H41" s="59" t="n">
+        <v>-161</v>
       </c>
       <c r="J41" s="30" t="n">
         <v>8</v>
@@ -6768,7 +6739,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M41" s="48" t="n">
+      <c r="M41" s="45" t="n">
         <v>102</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -6784,8 +6755,8 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q41" s="62" t="n">
-        <v>-136</v>
+      <c r="Q41" s="59" t="n">
+        <v>-134</v>
       </c>
     </row>
     <row r="42">
@@ -6794,32 +6765,32 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C42" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D42" s="48" t="n">
-        <v>5</v>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D42" s="45" t="n">
+        <v>4</v>
       </c>
       <c r="E42" s="30" t="n">
         <v>9</v>
       </c>
       <c r="F42" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="H42" s="62" t="n">
-        <v>-130</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="H42" s="59" t="n">
+        <v>-160</v>
       </c>
       <c r="J42" s="30" t="n">
         <v>9</v>
@@ -6834,7 +6805,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M42" s="48" t="n">
+      <c r="M42" s="45" t="n">
         <v>97</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -6850,7 +6821,7 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="Q42" s="62" t="n">
+      <c r="Q42" s="59" t="n">
         <v>-131</v>
       </c>
     </row>
@@ -6860,7 +6831,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C43" s="35" t="inlineStr">
@@ -6868,24 +6839,24 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D43" s="48" t="n">
-        <v>3</v>
+      <c r="D43" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F43" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="G43" s="38" t="inlineStr">
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H43" s="62" t="n">
-        <v>-119</v>
+      <c r="H43" s="59" t="n">
+        <v>-155</v>
       </c>
       <c r="J43" s="30" t="n">
         <v>10</v>
@@ -6900,7 +6871,7 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="M43" s="48" t="n">
+      <c r="M43" s="45" t="n">
         <v>92</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -6916,8 +6887,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q43" s="62" t="n">
-        <v>-124</v>
+      <c r="Q43" s="59" t="n">
+        <v>-126</v>
       </c>
     </row>
     <row r="44"/>
@@ -6927,121 +6898,121 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="59" t="inlineStr">
+      <c r="E45" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
       <c r="J45" s="25" t="inlineStr">
         <is>
-          <t>F8 보험</t>
-        </is>
-      </c>
-      <c r="N45" s="59" t="inlineStr">
+          <t>F8 기타법인</t>
+        </is>
+      </c>
+      <c r="N45" s="56" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="61" t="inlineStr">
+      <c r="E46" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="60" t="inlineStr">
+      <c r="J46" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="61" t="inlineStr">
+      <c r="N46" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="45" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="45" t="inlineStr">
+      <c r="F47" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="45" t="inlineStr">
+      <c r="G47" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="45" t="inlineStr">
+      <c r="K47" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="L47" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="45" t="inlineStr">
+      <c r="M47" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="45" t="inlineStr">
+      <c r="N47" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="45" t="inlineStr">
+      <c r="O47" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="45" t="inlineStr">
+      <c r="P47" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="45" t="inlineStr">
+      <c r="Q47" s="43" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -7061,7 +7032,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="48" t="n">
+      <c r="D48" s="45" t="n">
         <v>146</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -7077,7 +7048,7 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="H48" s="62" t="n">
+      <c r="H48" s="59" t="n">
         <v>-752</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -7085,7 +7056,7 @@
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="L48" s="35" t="inlineStr">
@@ -7093,24 +7064,24 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="48" t="n">
-        <v>63</v>
+      <c r="M48" s="45" t="n">
+        <v>9795</v>
       </c>
       <c r="N48" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O48" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="P48" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="Q48" s="62" t="n">
-        <v>-17</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="Q48" s="59" t="n">
+        <v>-37</v>
       </c>
     </row>
     <row r="49" ht="31" customHeight="1" s="15">
@@ -7122,12 +7093,12 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D49" s="48" t="n">
+      <c r="D49" s="45" t="n">
         <v>131</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -7143,7 +7114,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H49" s="62" t="n">
+      <c r="H49" s="59" t="n">
         <v>-602</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -7151,35 +7122,35 @@
       </c>
       <c r="K49" s="31" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="L49" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="M49" s="48" t="n">
-        <v>28</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M49" s="45" t="n">
+        <v>4028</v>
       </c>
       <c r="N49" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O49" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="P49" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="Q49" s="62" t="n">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="50" ht="31" customHeight="1" s="15">
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="Q49" s="59" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="30" t="n">
         <v>3</v>
       </c>
@@ -7193,7 +7164,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D50" s="48" t="n">
+      <c r="D50" s="45" t="n">
         <v>124</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -7209,7 +7180,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H50" s="62" t="n">
+      <c r="H50" s="59" t="n">
         <v>-422</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -7217,35 +7188,35 @@
       </c>
       <c r="K50" s="31" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="L50" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M50" s="48" t="n">
-        <v>23</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="M50" s="45" t="n">
+        <v>102</v>
       </c>
       <c r="N50" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O50" s="31" t="inlineStr">
         <is>
-          <t>기아</t>
-        </is>
-      </c>
-      <c r="P50" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="Q50" s="62" t="n">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="51" ht="31" customHeight="1" s="15">
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="P50" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="Q50" s="59" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="30" t="n">
         <v>4</v>
       </c>
@@ -7259,7 +7230,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D51" s="48" t="n">
+      <c r="D51" s="45" t="n">
         <v>115</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -7275,7 +7246,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H51" s="62" t="n">
+      <c r="H51" s="59" t="n">
         <v>-288</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -7283,16 +7254,16 @@
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
-        </is>
-      </c>
-      <c r="L51" s="38" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="M51" s="48" t="n">
-        <v>22</v>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="L51" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="M51" s="45" t="n">
+        <v>49</v>
       </c>
       <c r="N51" s="30" t="n">
         <v>4</v>
@@ -7307,8 +7278,8 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="Q51" s="62" t="n">
-        <v>-8</v>
+      <c r="Q51" s="59" t="n">
+        <v>-17</v>
       </c>
     </row>
     <row r="52" ht="31" customHeight="1" s="15">
@@ -7325,7 +7296,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D52" s="48" t="n">
+      <c r="D52" s="45" t="n">
         <v>88</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -7341,24 +7312,24 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H52" s="62" t="n">
+      <c r="H52" s="59" t="n">
         <v>-145</v>
       </c>
       <c r="J52" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="K52" s="17" t="inlineStr">
-        <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+      <c r="K52" s="31" t="inlineStr">
+        <is>
+          <t>두산</t>
         </is>
       </c>
       <c r="L52" s="35" t="inlineStr">
         <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="M52" s="48" t="n">
-        <v>20</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M52" s="45" t="n">
+        <v>37</v>
       </c>
       <c r="N52" s="30" t="n">
         <v>5</v>
@@ -7368,13 +7339,13 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="P52" s="38" t="inlineStr">
+      <c r="P52" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q52" s="62" t="n">
-        <v>-7</v>
+      <c r="Q52" s="59" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="53" ht="31" customHeight="1" s="15">
@@ -7391,7 +7362,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D53" s="48" t="n">
+      <c r="D53" s="45" t="n">
         <v>84</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -7402,12 +7373,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G53" s="38" t="inlineStr">
+      <c r="G53" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H53" s="62" t="n">
+      <c r="H53" s="59" t="n">
         <v>-122</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -7415,32 +7386,32 @@
       </c>
       <c r="K53" s="31" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="L53" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="M53" s="48" t="n">
-        <v>19</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M53" s="45" t="n">
+        <v>35</v>
       </c>
       <c r="N53" s="30" t="n">
         <v>6</v>
       </c>
       <c r="O53" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="P53" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="Q53" s="62" t="n">
-        <v>-6</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="Q53" s="59" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="54" ht="31" customHeight="1" s="15">
@@ -7457,7 +7428,7 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D54" s="48" t="n">
+      <c r="D54" s="45" t="n">
         <v>81</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -7468,12 +7439,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G54" s="38" t="inlineStr">
+      <c r="G54" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H54" s="62" t="n">
+      <c r="H54" s="59" t="n">
         <v>-78</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -7481,32 +7452,32 @@
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
-        </is>
-      </c>
-      <c r="L54" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="M54" s="48" t="n">
-        <v>16</v>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="L54" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="M54" s="45" t="n">
+        <v>29</v>
       </c>
       <c r="N54" s="30" t="n">
         <v>7</v>
       </c>
       <c r="O54" s="31" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="P54" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="Q54" s="62" t="n">
-        <v>-6</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="Q54" s="59" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="55">
@@ -7523,7 +7494,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D55" s="48" t="n">
+      <c r="D55" s="45" t="n">
         <v>79</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -7539,7 +7510,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H55" s="62" t="n">
+      <c r="H55" s="59" t="n">
         <v>-76</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -7547,35 +7518,35 @@
       </c>
       <c r="K55" s="31" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="L55" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="M55" s="48" t="n">
-        <v>15</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="M55" s="45" t="n">
+        <v>28</v>
       </c>
       <c r="N55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O55" s="31" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="P55" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="Q55" s="62" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="56">
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="Q55" s="59" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="56" ht="31" customHeight="1" s="15">
       <c r="A56" s="30" t="n">
         <v>9</v>
       </c>
@@ -7589,7 +7560,7 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D56" s="48" t="n">
+      <c r="D56" s="45" t="n">
         <v>76</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -7597,15 +7568,15 @@
       </c>
       <c r="F56" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="H56" s="62" t="n">
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="H56" s="59" t="n">
         <v>-69</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -7613,7 +7584,7 @@
       </c>
       <c r="K56" s="31" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="L56" s="35" t="inlineStr">
@@ -7621,24 +7592,24 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="M56" s="48" t="n">
-        <v>11</v>
+      <c r="M56" s="45" t="n">
+        <v>28</v>
       </c>
       <c r="N56" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O56" s="31" t="inlineStr">
         <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="P56" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="Q56" s="62" t="n">
-        <v>-5</v>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P56" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="Q56" s="59" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="57">
@@ -7655,7 +7626,7 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D57" s="48" t="n">
+      <c r="D57" s="45" t="n">
         <v>65</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -7663,15 +7634,15 @@
       </c>
       <c r="F57" s="31" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="H57" s="62" t="n">
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="H57" s="59" t="n">
         <v>-69</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -7679,44 +7650,451 @@
       </c>
       <c r="K57" s="31" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="L57" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="M57" s="48" t="n">
-        <v>10</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="M57" s="45" t="n">
+        <v>27</v>
       </c>
       <c r="N57" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O57" s="31" t="inlineStr">
         <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="P57" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="Q57" s="59" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59" ht="18" customHeight="1" s="15">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>F9 보험</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="inlineStr">
+        <is>
+          <t>주간 누적 · 억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="57" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="E60" s="58" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="43" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C61" s="43" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="E61" s="43" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="F61" s="43" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="G61" s="43" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="H61" s="43" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C62" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D62" s="45" t="n">
+        <v>63</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="31" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H62" s="59" t="n">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="C63" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D63" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="E63" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="31" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="G63" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H63" s="59" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="15">
+      <c r="A64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C64" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D64" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="31" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="G64" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="H64" s="59" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="65" ht="31" customHeight="1" s="15">
+      <c r="A65" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C65" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D65" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="E65" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="31" t="inlineStr">
+        <is>
+          <t>한국금융지주</t>
+        </is>
+      </c>
+      <c r="G65" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H65" s="59" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="A66" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>LIG디펜스앤에어로스페이스</t>
+        </is>
+      </c>
+      <c r="C66" s="35" t="inlineStr">
+        <is>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="D66" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
+        <is>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="G66" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="H66" s="59" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>메리츠금융지주</t>
+        </is>
+      </c>
+      <c r="C67" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D67" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="E67" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" s="31" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="G67" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="H67" s="59" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>삼성바이오로직스</t>
+        </is>
+      </c>
+      <c r="C68" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D68" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="E68" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>삼성물산</t>
+        </is>
+      </c>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="H68" s="59" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="C69" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D69" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="E69" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>대덕전자</t>
+        </is>
+      </c>
+      <c r="G69" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H69" s="59" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>코스메카코리아</t>
+        </is>
+      </c>
+      <c r="C70" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D70" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="H70" s="59" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>한화엔진</t>
+        </is>
+      </c>
+      <c r="C71" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
           <t>샘씨엔에스</t>
         </is>
       </c>
-      <c r="P57" s="35" t="inlineStr">
+      <c r="G71" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q57" s="62" t="n">
+      <c r="H71" s="59" t="n">
         <v>-4</v>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59" ht="31" customHeight="1" s="15">
-      <c r="A59" s="63" t="inlineStr">
-        <is>
-          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드 (확정 병합분) · 외인+기관=합산 카드와 동일</t>
+    <row r="72"/>
+    <row r="73" ht="31" customHeight="1" s="15">
+      <c r="A73" s="61" t="inlineStr">
+        <is>
+          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="39">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="E45:H45"/>
     <mergeCell ref="O1:Q1"/>
@@ -7724,7 +8102,7 @@
     <mergeCell ref="J31:M31"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A73:Q73"/>
     <mergeCell ref="J46:M46"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="J18:M18"/>
@@ -7734,7 +8112,9 @@
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="A1:M1"/>
@@ -7745,11 +8125,13 @@
     <mergeCell ref="N18:Q18"/>
     <mergeCell ref="J45:M45"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E60:H60"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="N17:Q17"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E59:H59"/>
     <mergeCell ref="J32:M32"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
@@ -7820,78 +8202,78 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>공매도 누적</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="43" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="43" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="43" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="43" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="43" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="43" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="P4" s="45" t="inlineStr">
+      <c r="P4" s="43" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="31" customHeight="1" s="15">
       <c r="A5" s="30" t="n">
         <v>1</v>
       </c>
@@ -7905,8 +8287,46 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="64" t="n">
-        <v>7736</v>
+      <c r="D5" s="62" t="n">
+        <v>7751</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="H5" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="I5" s="51" t="n">
+        <v>723.8</v>
+      </c>
+      <c r="J5" s="63" t="n">
+        <v>13145</v>
+      </c>
+      <c r="L5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="N5" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="O5" s="64" t="n">
+        <v>-14617.4</v>
+      </c>
+      <c r="P5" s="63" t="n">
+        <v>205396.7</v>
       </c>
     </row>
     <row r="6">
@@ -7923,8 +8343,46 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="64" t="n">
-        <v>3657</v>
+      <c r="D6" s="62" t="n">
+        <v>3677</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="I6" s="51" t="n">
+        <v>589.4</v>
+      </c>
+      <c r="J6" s="63" t="n">
+        <v>5479.1</v>
+      </c>
+      <c r="L6" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="N6" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="O6" s="64" t="n">
+        <v>-8156.2</v>
+      </c>
+      <c r="P6" s="63" t="n">
+        <v>223221.9</v>
       </c>
     </row>
     <row r="7">
@@ -7941,8 +8399,46 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="64" t="n">
-        <v>643</v>
+      <c r="D7" s="62" t="n">
+        <v>644</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="I7" s="51" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="J7" s="63" t="n">
+        <v>5628.1</v>
+      </c>
+      <c r="L7" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="31" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="N7" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="O7" s="64" t="n">
+        <v>-1780.6</v>
+      </c>
+      <c r="P7" s="63" t="n">
+        <v>27337.7</v>
       </c>
     </row>
     <row r="8">
@@ -7959,8 +8455,42 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="64" t="n">
+      <c r="D8" s="62" t="n">
         <v>523</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="I8" s="51" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="J8" s="63" t="n">
+        <v>7357.9</v>
+      </c>
+      <c r="L8" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="N8" s="35" t="inlineStr"/>
+      <c r="O8" s="64" t="n">
+        <v>-1435.9</v>
+      </c>
+      <c r="P8" s="63" t="n">
+        <v>26514</v>
       </c>
     </row>
     <row r="9">
@@ -7973,8 +8503,42 @@
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr"/>
-      <c r="D9" s="64" t="n">
+      <c r="D9" s="62" t="n">
         <v>435</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="I9" s="51" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="J9" s="63" t="n">
+        <v>6241.8</v>
+      </c>
+      <c r="L9" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" s="31" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="N9" s="35" t="inlineStr"/>
+      <c r="O9" s="64" t="n">
+        <v>-1292.1</v>
+      </c>
+      <c r="P9" s="63" t="n">
+        <v>29634.7</v>
       </c>
     </row>
     <row r="10" ht="31" customHeight="1" s="15">
@@ -7986,16 +8550,54 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D10" s="64" t="n">
+      <c r="D10" s="62" t="n">
         <v>368</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="F10" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="I10" s="51" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="J10" s="63" t="n">
+        <v>7805.8</v>
+      </c>
+      <c r="L10" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" s="31" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="N10" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="O10" s="64" t="n">
+        <v>-860.3</v>
+      </c>
+      <c r="P10" s="63" t="n">
+        <v>19002.7</v>
+      </c>
+    </row>
+    <row r="11" ht="31" customHeight="1" s="15">
       <c r="A11" s="30" t="n">
         <v>7</v>
       </c>
@@ -8009,8 +8611,46 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D11" s="64" t="n">
+      <c r="D11" s="62" t="n">
         <v>304</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="H11" s="60" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="I11" s="51" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="J11" s="63" t="n">
+        <v>7990.5</v>
+      </c>
+      <c r="L11" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="31" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="N11" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="O11" s="64" t="n">
+        <v>-750.5</v>
+      </c>
+      <c r="P11" s="63" t="n">
+        <v>12346.5</v>
       </c>
     </row>
     <row r="12">
@@ -8027,8 +8667,46 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D12" s="64" t="n">
-        <v>279</v>
+      <c r="D12" s="62" t="n">
+        <v>282</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="I12" s="51" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="J12" s="63" t="n">
+        <v>2761.3</v>
+      </c>
+      <c r="L12" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" s="31" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="N12" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="O12" s="64" t="n">
+        <v>-668.2</v>
+      </c>
+      <c r="P12" s="63" t="n">
+        <v>15587.3</v>
       </c>
     </row>
     <row r="13">
@@ -8045,8 +8723,46 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="64" t="n">
+      <c r="D13" s="62" t="n">
         <v>180</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="I13" s="51" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="J13" s="63" t="n">
+        <v>5185.7</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" s="31" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="N13" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="O13" s="64" t="n">
+        <v>-664.2</v>
+      </c>
+      <c r="P13" s="63" t="n">
+        <v>5242.8</v>
       </c>
     </row>
     <row r="14">
@@ -8063,13 +8779,51 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="D14" s="64" t="n">
+      <c r="D14" s="62" t="n">
         <v>172</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="I14" s="51" t="n">
+        <v>126</v>
+      </c>
+      <c r="J14" s="63" t="n">
+        <v>31977.3</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" s="31" t="inlineStr">
+        <is>
+          <t>두산</t>
+        </is>
+      </c>
+      <c r="N14" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="O14" s="64" t="n">
+        <v>-613.2</v>
+      </c>
+      <c r="P14" s="63" t="n">
+        <v>6549.8</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전주말 대비 최신 잔고</t>
         </is>
@@ -8094,7 +8848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20.5" customWidth="1" style="15" min="1" max="1"/>
@@ -8110,7 +8864,8 @@
     <col width="9.5" customWidth="1" style="15" min="11" max="11"/>
     <col width="9.5" customWidth="1" style="15" min="12" max="12"/>
     <col width="9.5" customWidth="1" style="15" min="13" max="13"/>
-    <col width="11.5" customWidth="1" style="15" min="14" max="14"/>
+    <col width="9.5" customWidth="1" style="15" min="14" max="14"/>
+    <col width="11.5" customWidth="1" style="15" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="15">
@@ -8158,74 +8913,80 @@
       </c>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="43" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="43" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="43" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="43" t="inlineStr">
+        <is>
+          <t>기타법인</t>
+        </is>
+      </c>
+      <c r="M4" s="43" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="N4" s="43" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="O4" s="43" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -8267,13 +9028,16 @@
       <c r="K5" s="68" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="69" t="n">
+      <c r="L5" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="67" t="n">
-        <v>-4</v>
-      </c>
-      <c r="N5" s="30" t="inlineStr"/>
+      <c r="N5" s="67" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O5" s="30" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -8297,13 +9061,13 @@
         <v>60</v>
       </c>
       <c r="G6" s="68" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H6" s="68" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="J6" s="68" t="n">
         <v>26</v>
@@ -8311,13 +9075,16 @@
       <c r="K6" s="68" t="n">
         <v>210</v>
       </c>
-      <c r="L6" s="68" t="n">
+      <c r="L6" s="67" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M6" s="68" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="67" t="n">
+      <c r="N6" s="67" t="n">
         <v>-279</v>
       </c>
-      <c r="N6" s="60" t="inlineStr">
+      <c r="O6" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -8348,7 +9115,7 @@
         <v>26</v>
       </c>
       <c r="H7" s="68" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I7" s="67" t="n">
         <v>-5</v>
@@ -8359,13 +9126,16 @@
       <c r="K7" s="68" t="n">
         <v>24</v>
       </c>
-      <c r="L7" s="68" t="n">
+      <c r="L7" s="67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M7" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="67" t="n">
-        <v>-112</v>
-      </c>
-      <c r="N7" s="70" t="inlineStr">
+      <c r="N7" s="67" t="n">
+        <v>-111</v>
+      </c>
+      <c r="O7" s="70" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -8390,16 +9160,16 @@
         <v>0.46</v>
       </c>
       <c r="F8" s="68" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G8" s="68" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8" s="68" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>-63</v>
+        <v>-65</v>
       </c>
       <c r="J8" s="68" t="n">
         <v>165</v>
@@ -8407,13 +9177,16 @@
       <c r="K8" s="68" t="n">
         <v>71</v>
       </c>
-      <c r="L8" s="68" t="n">
+      <c r="L8" s="67" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M8" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="67" t="n">
-        <v>-272</v>
-      </c>
-      <c r="N8" s="30" t="inlineStr"/>
+      <c r="N8" s="67" t="n">
+        <v>-267</v>
+      </c>
+      <c r="O8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -8437,13 +9210,13 @@
         <v>152</v>
       </c>
       <c r="G9" s="67" t="n">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="H9" s="68" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>-100</v>
+        <v>-103</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>-66</v>
@@ -8452,12 +9225,15 @@
         <v>95</v>
       </c>
       <c r="L9" s="68" t="n">
+        <v>146</v>
+      </c>
+      <c r="M9" s="68" t="n">
         <v>27</v>
       </c>
-      <c r="M9" s="67" t="n">
-        <v>-260</v>
-      </c>
-      <c r="N9" s="30" t="inlineStr"/>
+      <c r="N9" s="67" t="n">
+        <v>-256</v>
+      </c>
+      <c r="O9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -8481,13 +9257,13 @@
         <v>118</v>
       </c>
       <c r="G10" s="67" t="n">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="H10" s="68" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" s="68" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J10" s="67" t="n">
         <v>-155</v>
@@ -8495,13 +9271,16 @@
       <c r="K10" s="68" t="n">
         <v>55</v>
       </c>
-      <c r="L10" s="69" t="n">
+      <c r="L10" s="67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M10" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="67" t="n">
-        <v>-75</v>
-      </c>
-      <c r="N10" s="30" t="inlineStr"/>
+      <c r="N10" s="67" t="n">
+        <v>-74</v>
+      </c>
+      <c r="O10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -8540,12 +9319,15 @@
         <v>0</v>
       </c>
       <c r="L11" s="67" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M11" s="67" t="n">
         <v>-1</v>
       </c>
-      <c r="M11" s="67" t="n">
+      <c r="N11" s="67" t="n">
         <v>-32</v>
       </c>
-      <c r="N11" s="30" t="inlineStr"/>
+      <c r="O11" s="30" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -8586,10 +9368,13 @@
       <c r="L12" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="67" t="n">
+      <c r="M12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="67" t="n">
         <v>-1</v>
       </c>
-      <c r="N12" s="30" t="inlineStr"/>
+      <c r="O12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -8627,13 +9412,16 @@
       <c r="K13" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="69" t="n">
+      <c r="L13" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="68" t="n">
+      <c r="N13" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="N13" s="61" t="inlineStr">
+      <c r="O13" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -8658,16 +9446,16 @@
         <v>-0.26</v>
       </c>
       <c r="F14" s="68" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G14" s="67" t="n">
-        <v>-401</v>
+        <v>-414</v>
       </c>
       <c r="H14" s="68" t="n">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>-453</v>
+        <v>-466</v>
       </c>
       <c r="J14" s="68" t="n">
         <v>74</v>
@@ -8676,16 +9464,15 @@
         <v>-43</v>
       </c>
       <c r="L14" s="68" t="n">
+        <v>53</v>
+      </c>
+      <c r="M14" s="68" t="n">
         <v>27</v>
       </c>
-      <c r="M14" s="67" t="n">
-        <v>-253</v>
-      </c>
-      <c r="N14" s="70" t="inlineStr">
-        <is>
-          <t>수급유입</t>
-        </is>
-      </c>
+      <c r="N14" s="67" t="n">
+        <v>-238</v>
+      </c>
+      <c r="O14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -8709,13 +9496,13 @@
         <v>196</v>
       </c>
       <c r="G15" s="68" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H15" s="68" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I15" s="67" t="n">
-        <v>-157</v>
+        <v>-160</v>
       </c>
       <c r="J15" s="68" t="n">
         <v>136</v>
@@ -8724,12 +9511,15 @@
         <v>42</v>
       </c>
       <c r="L15" s="68" t="n">
+        <v>109</v>
+      </c>
+      <c r="M15" s="68" t="n">
         <v>23</v>
       </c>
-      <c r="M15" s="67" t="n">
-        <v>-353</v>
-      </c>
-      <c r="N15" s="70" t="inlineStr">
+      <c r="N15" s="67" t="n">
+        <v>-351</v>
+      </c>
+      <c r="O15" s="70" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -8754,13 +9544,13 @@
         <v>-0.32</v>
       </c>
       <c r="F16" s="68" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G16" s="67" t="n">
-        <v>-60</v>
+        <v>-61</v>
       </c>
       <c r="H16" s="68" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I16" s="67" t="n">
         <v>-8</v>
@@ -8771,13 +9561,16 @@
       <c r="K16" s="67" t="n">
         <v>-23</v>
       </c>
-      <c r="L16" s="67" t="n">
+      <c r="L16" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="67" t="n">
         <v>-5</v>
       </c>
-      <c r="M16" s="67" t="n">
-        <v>-73</v>
-      </c>
-      <c r="N16" s="70" t="inlineStr">
+      <c r="N16" s="67" t="n">
+        <v>-74</v>
+      </c>
+      <c r="O16" s="70" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -8802,16 +9595,16 @@
         <v>-0.93</v>
       </c>
       <c r="F17" s="67" t="n">
-        <v>-316</v>
+        <v>-315</v>
       </c>
       <c r="G17" s="68" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="67" t="n">
         <v>-273</v>
       </c>
       <c r="I17" s="67" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="J17" s="69" t="n">
         <v>0</v>
@@ -8819,13 +9612,16 @@
       <c r="K17" s="68" t="n">
         <v>155</v>
       </c>
-      <c r="L17" s="68" t="n">
+      <c r="L17" s="67" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M17" s="68" t="n">
         <v>20</v>
       </c>
-      <c r="M17" s="68" t="n">
+      <c r="N17" s="68" t="n">
         <v>279</v>
       </c>
-      <c r="N17" s="30" t="inlineStr"/>
+      <c r="O17" s="30" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
@@ -8849,13 +9645,13 @@
         <v>282</v>
       </c>
       <c r="G18" s="67" t="n">
-        <v>-168</v>
+        <v>-171</v>
       </c>
       <c r="H18" s="68" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I18" s="67" t="n">
-        <v>-50</v>
+        <v>-54</v>
       </c>
       <c r="J18" s="67" t="n">
         <v>-149</v>
@@ -8863,13 +9659,16 @@
       <c r="K18" s="68" t="n">
         <v>27</v>
       </c>
-      <c r="L18" s="68" t="n">
+      <c r="L18" s="67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M18" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="67" t="n">
-        <v>-110</v>
-      </c>
-      <c r="N18" s="70" t="inlineStr">
+      <c r="N18" s="67" t="n">
+        <v>-109</v>
+      </c>
+      <c r="O18" s="70" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -8894,30 +9693,33 @@
         <v>-1.17</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>-564</v>
+        <v>-561</v>
       </c>
       <c r="G19" s="68" t="n">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="I19" s="67" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="J19" s="68" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K19" s="68" t="n">
         <v>155</v>
       </c>
       <c r="L19" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" s="68" t="n">
         <v>34</v>
       </c>
-      <c r="M19" s="68" t="n">
-        <v>135</v>
-      </c>
-      <c r="N19" s="61" t="inlineStr">
+      <c r="N19" s="68" t="n">
+        <v>137</v>
+      </c>
+      <c r="O19" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -8942,16 +9744,16 @@
         <v>-1.18</v>
       </c>
       <c r="F20" s="67" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G20" s="68" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H20" s="67" t="n">
-        <v>-79</v>
+        <v>-83</v>
       </c>
       <c r="I20" s="67" t="n">
-        <v>-90</v>
+        <v>-93</v>
       </c>
       <c r="J20" s="68" t="n">
         <v>127</v>
@@ -8960,12 +9762,15 @@
         <v>115</v>
       </c>
       <c r="L20" s="68" t="n">
+        <v>153</v>
+      </c>
+      <c r="M20" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="67" t="n">
-        <v>-74</v>
-      </c>
-      <c r="N20" s="30" t="inlineStr"/>
+      <c r="N20" s="67" t="n">
+        <v>-70</v>
+      </c>
+      <c r="O20" s="30" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -8986,16 +9791,16 @@
         <v>-1.4</v>
       </c>
       <c r="F21" s="67" t="n">
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="G21" s="67" t="n">
-        <v>-673</v>
+        <v>-695</v>
       </c>
       <c r="H21" s="67" t="n">
-        <v>-747</v>
+        <v>-770</v>
       </c>
       <c r="I21" s="67" t="n">
-        <v>-683</v>
+        <v>-706</v>
       </c>
       <c r="J21" s="67" t="n">
         <v>-131</v>
@@ -9004,12 +9809,15 @@
         <v>-110</v>
       </c>
       <c r="L21" s="68" t="n">
+        <v>20</v>
+      </c>
+      <c r="M21" s="68" t="n">
         <v>46</v>
       </c>
-      <c r="M21" s="68" t="n">
-        <v>722</v>
-      </c>
-      <c r="N21" s="61" t="inlineStr">
+      <c r="N21" s="68" t="n">
+        <v>749</v>
+      </c>
+      <c r="O21" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -9051,13 +9859,16 @@
       <c r="K22" s="68" t="n">
         <v>12</v>
       </c>
-      <c r="L22" s="69" t="n">
+      <c r="L22" s="67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M22" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="67" t="n">
+      <c r="N22" s="67" t="n">
         <v>-2</v>
       </c>
-      <c r="N22" s="30" t="inlineStr"/>
+      <c r="O22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
@@ -9078,16 +9889,16 @@
         <v>-1.82</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>-137</v>
+        <v>-139</v>
       </c>
       <c r="G23" s="68" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>-42</v>
+        <v>-47</v>
       </c>
       <c r="I23" s="67" t="n">
-        <v>-23</v>
+        <v>-26</v>
       </c>
       <c r="J23" s="68" t="n">
         <v>25</v>
@@ -9096,12 +9907,15 @@
         <v>84</v>
       </c>
       <c r="L23" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="M23" s="68" t="n">
-        <v>35</v>
-      </c>
-      <c r="N23" s="30" t="inlineStr"/>
+      <c r="N23" s="68" t="n">
+        <v>41</v>
+      </c>
+      <c r="O23" s="30" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
@@ -9125,10 +9939,10 @@
         <v>-64</v>
       </c>
       <c r="G24" s="67" t="n">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="H24" s="67" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="I24" s="67" t="n">
         <v>-31</v>
@@ -9139,13 +9953,16 @@
       <c r="K24" s="67" t="n">
         <v>-29</v>
       </c>
-      <c r="L24" s="68" t="n">
+      <c r="L24" s="67" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M24" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="M24" s="68" t="n">
+      <c r="N24" s="68" t="n">
         <v>135</v>
       </c>
-      <c r="N24" s="61" t="inlineStr">
+      <c r="O24" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -9170,16 +9987,16 @@
         <v>-2.92</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>-435</v>
+        <v>-429</v>
       </c>
       <c r="G25" s="67" t="n">
-        <v>-602</v>
+        <v>-605</v>
       </c>
       <c r="H25" s="67" t="n">
-        <v>-1038</v>
+        <v>-1034</v>
       </c>
       <c r="I25" s="67" t="n">
-        <v>-360</v>
+        <v>-363</v>
       </c>
       <c r="J25" s="67" t="n">
         <v>-60</v>
@@ -9187,13 +10004,16 @@
       <c r="K25" s="67" t="n">
         <v>-191</v>
       </c>
-      <c r="L25" s="68" t="n">
+      <c r="L25" s="67" t="n">
+        <v>-27</v>
+      </c>
+      <c r="M25" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="M25" s="68" t="n">
-        <v>1064</v>
-      </c>
-      <c r="N25" s="30" t="inlineStr"/>
+      <c r="N25" s="68" t="n">
+        <v>1061</v>
+      </c>
+      <c r="O25" s="30" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -9214,30 +10034,33 @@
         <v>-3.85</v>
       </c>
       <c r="F26" s="67" t="n">
-        <v>-32476</v>
+        <v>-32978</v>
       </c>
       <c r="G26" s="67" t="n">
-        <v>-10896</v>
+        <v>-11063</v>
       </c>
       <c r="H26" s="67" t="n">
-        <v>-43372</v>
+        <v>-44040</v>
       </c>
       <c r="I26" s="67" t="n">
-        <v>-4211</v>
+        <v>-4366</v>
       </c>
       <c r="J26" s="67" t="n">
-        <v>-5796</v>
+        <v>-5808</v>
       </c>
       <c r="K26" s="67" t="n">
         <v>-1054</v>
       </c>
       <c r="L26" s="68" t="n">
+        <v>14627</v>
+      </c>
+      <c r="M26" s="68" t="n">
         <v>170</v>
       </c>
-      <c r="M26" s="68" t="n">
-        <v>28769</v>
-      </c>
-      <c r="N26" s="61" t="inlineStr">
+      <c r="N26" s="68" t="n">
+        <v>29414</v>
+      </c>
+      <c r="O26" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -9262,16 +10085,16 @@
         <v>-4.1</v>
       </c>
       <c r="F27" s="67" t="n">
-        <v>-276</v>
+        <v>-270</v>
       </c>
       <c r="G27" s="67" t="n">
         <v>-291</v>
       </c>
       <c r="H27" s="67" t="n">
-        <v>-567</v>
+        <v>-561</v>
       </c>
       <c r="I27" s="67" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="J27" s="67" t="n">
         <v>-42</v>
@@ -9279,13 +10102,16 @@
       <c r="K27" s="67" t="n">
         <v>-95</v>
       </c>
-      <c r="L27" s="67" t="n">
+      <c r="L27" s="68" t="n">
+        <v>108</v>
+      </c>
+      <c r="M27" s="67" t="n">
         <v>-4</v>
       </c>
-      <c r="M27" s="68" t="n">
-        <v>459</v>
-      </c>
-      <c r="N27" s="30" t="inlineStr"/>
+      <c r="N27" s="68" t="n">
+        <v>453</v>
+      </c>
+      <c r="O27" s="30" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
@@ -9306,30 +10132,33 @@
         <v>-4.75</v>
       </c>
       <c r="F28" s="67" t="n">
-        <v>-32466</v>
+        <v>-32973</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>-10553</v>
+        <v>-10692</v>
       </c>
       <c r="H28" s="67" t="n">
-        <v>-43019</v>
+        <v>-43664</v>
       </c>
       <c r="I28" s="67" t="n">
-        <v>-2880</v>
+        <v>-3007</v>
       </c>
       <c r="J28" s="67" t="n">
-        <v>-6491</v>
+        <v>-6503</v>
       </c>
       <c r="K28" s="67" t="n">
         <v>-1206</v>
       </c>
       <c r="L28" s="68" t="n">
+        <v>14337</v>
+      </c>
+      <c r="M28" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="M28" s="68" t="n">
-        <v>28713</v>
-      </c>
-      <c r="N28" s="61" t="inlineStr">
+      <c r="N28" s="68" t="n">
+        <v>29327</v>
+      </c>
+      <c r="O28" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -9351,12 +10180,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N28"/>
+  <autoFilter ref="A4:O28"/>
   <mergeCells count="4">
-    <mergeCell ref="L1:N1"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A30:O30"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B28">
     <cfRule type="dataBar" priority="1">
@@ -9367,7 +10196,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AD64E6BE-00B7-4888-831C-534620C87092}</x14:id>
+          <x14:id>{2032545E-31CB-476A-9A50-C610257E2F0C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9381,7 +10210,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07E17536-B97F-4545-9FE1-0C5FCAF039D3}</x14:id>
+          <x14:id>{AAB57F4F-0CE1-4F07-B9CB-5D5E52CBCB20}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9395,7 +10224,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{619E664A-D084-4440-94BB-9175ECAE0A61}</x14:id>
+          <x14:id>{3D87C0C5-28A2-45A3-86C0-B1FFEA6295E3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9409,7 +10238,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DCD41596-2DDB-4A70-B81C-934C66CDA163}</x14:id>
+          <x14:id>{193057F8-B4A1-4044-82E1-6FE10A9D496F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9419,7 +10248,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AD64E6BE-00B7-4888-831C-534620C87092}">
+          <x14:cfRule type="dataBar" id="{2032545E-31CB-476A-9A50-C610257E2F0C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -9432,7 +10261,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07E17536-B97F-4545-9FE1-0C5FCAF039D3}">
+          <x14:cfRule type="dataBar" id="{AAB57F4F-0CE1-4F07-B9CB-5D5E52CBCB20}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -9445,7 +10274,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{619E664A-D084-4440-94BB-9175ECAE0A61}">
+          <x14:cfRule type="dataBar" id="{3D87C0C5-28A2-45A3-86C0-B1FFEA6295E3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -9458,7 +10287,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DCD41596-2DDB-4A70-B81C-934C66CDA163}">
+          <x14:cfRule type="dataBar" id="{193057F8-B4A1-4044-82E1-6FE10A9D496F}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/weekly_briefing/2026-09-14.xlsx
+++ b/public/reports/weekly_briefing/2026-09-14.xlsx
@@ -932,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14 22:50 KST</t>
+          <t>2026-09-14 23:03 KST</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>AI 속도조절론 부각에 따른 반도체 급락과 외국인 대규모 매도</t>
+          <t>미국발 AI 속도조절론과 외국인 대규모 매도세에 따른 코스피 급락</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>미국 증시는 CPI 예상치 부합으로 상승했으나, 국내 증시는 'AI 속도조절론'이 부각되며 반도체 중심의 외국인 매도세가 쏟아져 급락함.</t>
+          <t>미국 증시의 기술주 반등과 CPI 예상치 부합에도 불구하고, 국내 증시는 미국발 'AI 속도조절론'이 부각되며 반도체 대형주 중심의 외국인 매도세가 쏟아져 급락함.</t>
         </is>
       </c>
     </row>
@@ -1720,21 +1720,21 @@
     <row r="37" ht="31" customHeight="1" s="15">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>- 미국 8월 CPI는 3.4%로 예상치에 부합했으나, 미시간대 소비자심리지수는 47.8로 예상치(51.0)를 하회하며 매크로 환경의 불확실성이 잔존함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="15">
+          <t>- 미국 8월 소비자물가지수(CPI)는 전년 대비 3.4%로 예상치에 부합하며 인플레이션 둔화 경로를 재확인했으나, 미시간대 소비자심리지수는 47.8로 예상치(51.0)를 하회하며 소비 심리 위축을 시사함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="31" customHeight="1" s="15">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서 외국인은 전기·전자 섹터에 매도를 집중하며 코스피 3.3조 원 순매도를 기록, 지수 하락의 핵심 동인으로 작용함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="15">
+          <t>- 수급 측면에서 코스피는 외국인 -32,875억 원, 기관 -11,742억 원의 동반 매도세가 지수를 끌어내렸으며, 특히 전기·전자 섹터에 외국인 매물이 집중됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="31" customHeight="1" s="15">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 지표보다 AI 산업에 대한 센티먼트 변화가 시장 수급을 지배하는 국면임.</t>
+          <t>- 매크로 환경의 불확실성과 반도체 섹터에 대한 수급 이탈이 겹치며 지수 하락을 주도했으므로, 향후 외국인 매도세 진정 여부와 수출입 확정치가 증시 반등의 핵심 변수가 될 것임.</t>
         </is>
       </c>
     </row>
@@ -3082,197 +3082,141 @@
     <row r="93" ht="15" customHeight="1" s="15">
       <c r="A93" s="17" t="inlineStr">
         <is>
-          <t>- 코스피는 외국인의 3.3조 원 규모 매도세가 쏟아지며 전일 대비 3.26% 급락한 6684.37에 마감함.</t>
+          <t>- 코스피는 외국인의 3.3조 원 규모 대규모 매도세가 쏟아지며 전일 대비 3.26% 급락한 6684.37에 마감함.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="15">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>- 코스닥 역시 투자 심리 위축으로 1.69% 하락하며 동반 약세를 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="15">
+          <t>- 코스닥 역시 1.69% 하락하며 투자 심리가 크게 위축됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="31" customHeight="1" s="15">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t>- 미국발 'AI 속도조절론'이 부각되면서 전기·전자 섹터에 외국인 매물이 집중되어 지수 하락을 주도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="15">
+          <t>- 전기·전자 섹터는 미국발 'AI 속도조절론'이 부각되면서 삼성전자와 SK하이닉스에 외국인 매물이 집중되어 각각 3%와 6%대 급락하며 지수 하락의 핵심 원인이 됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="31" customHeight="1" s="15">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>- 반면 방산 및 조선 섹터는 연이은 수주 계약 성공으로 상대적 견조함을 유지함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+          <t>- 시장 전반의 약세 속에서도 운송·창고 섹터는 중동 지정학적 리스크에 따른 해운 운임 상승 기대감과 통합 항공사 출범 이슈로 견조한 흐름을 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="15">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>- 외국인과 기관의 동반 매도세가 지수 하락을 주도함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>섹터·테마 흐름</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr"/>
-      <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="3" t="inlineStr"/>
-      <c r="G98" s="3" t="inlineStr"/>
-      <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr"/>
-      <c r="J98" s="3" t="inlineStr"/>
-      <c r="K98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="15">
-      <c r="A99" s="17" t="inlineStr">
-        <is>
-          <t>- 전기·전자 섹터는 AI 관련 우려로 외국인 매물이 집중되며 급락세 지속.</t>
-        </is>
-      </c>
+      <c r="C99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="15">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>- 운송·창고 및 오락·문화 섹터는 개별 이슈와 수급 유입으로 방어적 흐름을 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101"/>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+          <t>- 전기·전자 섹터는 미국발 AI 속도조절론 부각으로 외국인 매물이 집중되며 급락함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="15">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>- 운송·창고 섹터는 지정학적 리스크와 통합 항공사 이슈로 견조한 흐름을 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="15">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>- 오락·문화 섹터는 글로벌 IP 파워 기대감으로 상승하며 방어적 성격을 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr"/>
-      <c r="D102" s="3" t="inlineStr"/>
-      <c r="E102" s="3" t="inlineStr"/>
-      <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
-      <c r="H102" s="3" t="inlineStr"/>
-      <c r="I102" s="3" t="inlineStr"/>
-      <c r="J102" s="18" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="K104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="31" customHeight="1" s="15">
-      <c r="A104" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>인피니트헬스케어</t>
-        </is>
-      </c>
-      <c r="C104" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D104" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F104" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="G104" s="17" t="inlineStr">
-        <is>
-          <t>654억 원 규모의 대규모 현금배당 계획 발표.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="15">
-      <c r="A105" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B105" s="31" t="inlineStr">
-        <is>
-          <t>한국첨단소재</t>
-        </is>
-      </c>
-      <c r="C105" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D105" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E105" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F105" s="28" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>차세대 광통신 기술 검증 및 양자통신 클러스터 참여.</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3228,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>인피니트헬스케어</t>
         </is>
       </c>
       <c r="C106" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -3303,11 +3247,11 @@
         </is>
       </c>
       <c r="F106" s="28" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>K9 자주포 및 천무 등 연이은 수출 계약 성공.</t>
+          <t>654억 원 규모의 대규모 현금배당 계획 발표.</t>
         </is>
       </c>
     </row>
@@ -3319,134 +3263,197 @@
       </c>
       <c r="B107" s="31" t="inlineStr">
         <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D107" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F107" s="28" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>차세대 광통신 기술 검증 및 양자통신 클러스터 참여.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="31" customHeight="1" s="15">
+      <c r="A108" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="C108" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D108" s="35" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F108" s="28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>K9 자주포 및 천무 등 연이은 수출 계약 성공.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="15">
+      <c r="A109" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B109" s="31" t="inlineStr">
+        <is>
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="C107" s="31" t="inlineStr">
+      <c r="C109" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
+      <c r="D109" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E107" s="14" t="inlineStr">
+      <c r="E109" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F107" s="28" t="n">
+      <c r="F109" s="28" t="n">
         <v>3.27</v>
       </c>
-      <c r="G107" s="17" t="inlineStr">
+      <c r="G109" s="17" t="inlineStr">
         <is>
           <t>LNG선 4척 추가 수주를 통한 신규 수주 물량 확보.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" s="15">
-      <c r="A108" s="31" t="inlineStr">
+    <row r="110" ht="15" customHeight="1" s="15">
+      <c r="A110" s="31" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B108" s="31" t="inlineStr">
+      <c r="B110" s="31" t="inlineStr">
         <is>
           <t>영풍</t>
         </is>
       </c>
-      <c r="C108" s="31" t="inlineStr">
+      <c r="C110" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
+      <c r="D110" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="E108" s="14" t="inlineStr">
+      <c r="E110" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F108" s="28" t="n">
+      <c r="F110" s="28" t="n">
         <v>0.3</v>
       </c>
-      <c r="G108" s="17" t="inlineStr">
+      <c r="G110" s="17" t="inlineStr">
         <is>
           <t>계열사의 북미 빅테크향 고다층 인쇄회로기판 공급 계약.</t>
         </is>
       </c>
     </row>
-    <row r="109"/>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr"/>
-      <c r="D110" s="3" t="inlineStr"/>
-      <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" s="3" t="inlineStr"/>
-      <c r="G110" s="3" t="inlineStr"/>
-      <c r="H110" s="3" t="inlineStr"/>
-      <c r="I110" s="3" t="inlineStr"/>
-      <c r="J110" s="3" t="inlineStr"/>
-      <c r="K110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111" ht="15" customHeight="1" s="15">
-      <c r="A111" s="17" t="inlineStr">
-        <is>
-          <t>- 반도체 섹터 외국인 매도 진정 시 기술적 반등 전개</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1" s="15">
-      <c r="A112" s="17" t="inlineStr">
-        <is>
-          <t>- AI 속도조절론 지속에 따른 외국인 추가 이탈 시 하방 압력 확대</t>
-        </is>
-      </c>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
     </row>
     <row r="113" ht="15" customHeight="1" s="15">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 반도체 섹터 순매수 전환 여부</t>
+          <t>- 외국인 매도세 진정 및 반도체 대형주 수급 개선 시 지수 기술적 반등 전개</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="15">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>- FOMC 기준금리 결정</t>
+          <t>- AI 속도조절론 지속 및 외국인 매도세 지속 시 추가 하방 압력 발생</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="15">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>- 무역수지</t>
+          <t>- 외국인의 반도체 대형주 순매수 전환 여부</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="15">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>- 미국 소매판매</t>
+          <t>- 무역수지 및 수출입 확정치(9/15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1" s="15">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 FOMC 기준금리 결정(9/17)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A114:K114"/>
     <mergeCell ref="G105:K105"/>
@@ -3465,39 +3472,40 @@
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A78:E78"/>
-    <mergeCell ref="G103:K103"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A99:K99"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="G69:K69"/>
     <mergeCell ref="A37:K37"/>
     <mergeCell ref="G87:K87"/>
     <mergeCell ref="A89:K89"/>
     <mergeCell ref="G83:K83"/>
+    <mergeCell ref="A101:K101"/>
     <mergeCell ref="G108:K108"/>
     <mergeCell ref="A95:K95"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="G33:K33"/>
     <mergeCell ref="A113:K113"/>
-    <mergeCell ref="G104:K104"/>
     <mergeCell ref="G65:K65"/>
+    <mergeCell ref="G110:K110"/>
     <mergeCell ref="G79:K79"/>
     <mergeCell ref="A116:K116"/>
     <mergeCell ref="G73:K73"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A97:K97"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="A100:K100"/>
     <mergeCell ref="A96:K96"/>
+    <mergeCell ref="G109:K109"/>
     <mergeCell ref="G85:K85"/>
-    <mergeCell ref="A112:K112"/>
     <mergeCell ref="G32:K32"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A115:K115"/>
+    <mergeCell ref="A117:K117"/>
     <mergeCell ref="A93:K93"/>
     <mergeCell ref="G106:K106"/>
     <mergeCell ref="C4:K4"/>
+    <mergeCell ref="A102:K102"/>
     <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A111:K111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10196,7 +10204,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2032545E-31CB-476A-9A50-C610257E2F0C}</x14:id>
+          <x14:id>{CEC25292-303F-4ED8-B2DD-6FBE6AFD0998}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10210,7 +10218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AAB57F4F-0CE1-4F07-B9CB-5D5E52CBCB20}</x14:id>
+          <x14:id>{53793DF9-B62B-405F-8151-B7EC148EA032}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10224,7 +10232,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3D87C0C5-28A2-45A3-86C0-B1FFEA6295E3}</x14:id>
+          <x14:id>{863BFD9F-EB08-4A7B-8250-41FAA248D6DB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10238,7 +10246,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{193057F8-B4A1-4044-82E1-6FE10A9D496F}</x14:id>
+          <x14:id>{B30D9CB4-9A45-4B18-B899-D6DD8F565016}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10248,7 +10256,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2032545E-31CB-476A-9A50-C610257E2F0C}">
+          <x14:cfRule type="dataBar" id="{CEC25292-303F-4ED8-B2DD-6FBE6AFD0998}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -10261,7 +10269,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AAB57F4F-0CE1-4F07-B9CB-5D5E52CBCB20}">
+          <x14:cfRule type="dataBar" id="{53793DF9-B62B-405F-8151-B7EC148EA032}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -10274,7 +10282,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3D87C0C5-28A2-45A3-86C0-B1FFEA6295E3}">
+          <x14:cfRule type="dataBar" id="{863BFD9F-EB08-4A7B-8250-41FAA248D6DB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -10287,7 +10295,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{193057F8-B4A1-4044-82E1-6FE10A9D496F}">
+          <x14:cfRule type="dataBar" id="{B30D9CB4-9A45-4B18-B899-D6DD8F565016}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
